--- a/Requirements-Analysis/Affinity_Traceability_Analysis_Tiimo.xlsx
+++ b/Requirements-Analysis/Affinity_Traceability_Analysis_Tiimo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chitrangidoshi/Documents/Buisness Analyst/Case Study/Tiimo/Requirement Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77CA2B54-1D89-2A41-BE92-C4CFBBB21C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B1413A-B03C-594A-BBDB-68125FD955B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{A9674CC6-0D77-DC4F-B371-451AB74EFA0F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{A9674CC6-0D77-DC4F-B371-451AB74EFA0F}"/>
   </bookViews>
   <sheets>
     <sheet name="Analysis" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="38" r:id="rId4"/>
+    <pivotCache cacheId="40" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="322">
   <si>
     <t>Source</t>
   </si>
@@ -1054,12 +1054,15 @@
       <t xml:space="preserve"> Req_Group/Req_ID mapped via Requirements‑Catalog‑Tiimo.xlsx. Primary_Req_ID ‘Future’ = post‑MVP backlog, not dropped.</t>
     </r>
   </si>
+  <si>
+    <t>REQUIREMENTS AFFINITY AND TRACEABILITY TABLE - TIIMO IPHONE CHURN REDUCTION</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1161,6 +1164,13 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1304,7 +1314,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1370,6 +1380,9 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Heading 1" xfId="1" builtinId="16"/>
@@ -1385,53 +1398,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.749992370372631"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.749992370372631"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1622,6 +1588,53 @@
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FFB9B4FF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.749992370372631"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.749992370372631"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -7820,7 +7833,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C49BA34E-92BB-5D4D-811E-C3031738A9DF}" name="PivotTable5" cacheId="38" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C49BA34E-92BB-5D4D-811E-C3031738A9DF}" name="PivotTable5" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="A84:J121" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField dataField="1" showAll="0"/>
@@ -8492,7 +8505,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{52AB4ED5-C7E0-8B4F-9714-5AD1125F1803}" name="PivotTable3" cacheId="38" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{52AB4ED5-C7E0-8B4F-9714-5AD1125F1803}" name="PivotTable3" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
   <location ref="A131:B145" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="11">
     <pivotField dataField="1" showAll="0"/>
@@ -9072,7 +9085,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D92E3B1F-A9C2-5F47-954E-BEC4DF1471DC}" name="PivotTable4" cacheId="38" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D92E3B1F-A9C2-5F47-954E-BEC4DF1471DC}" name="PivotTable4" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="A51:K59" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="11">
     <pivotField dataField="1" showAll="0"/>
@@ -9521,29 +9534,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3671B8E3-831C-2944-92F7-2BA71D57EBB5}" name="Table_Affinity_Analysis" displayName="Table_Affinity_Analysis" ref="A1:K114" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14" headerRowCellStyle="Heading 1">
-  <autoFilter ref="A1:K114" xr:uid="{3671B8E3-831C-2944-92F7-2BA71D57EBB5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3671B8E3-831C-2944-92F7-2BA71D57EBB5}" name="Table_Affinity_Analysis" displayName="Table_Affinity_Analysis" ref="A3:K116" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12" headerRowCellStyle="Heading 1">
+  <autoFilter ref="A3:K116" xr:uid="{3671B8E3-831C-2944-92F7-2BA71D57EBB5}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{D8B7633B-220A-7845-A647-D85993E95A37}" name="Review_Id" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{19086F0C-CE61-CC49-8DCF-68D95499EB1C}" name="Source" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{93741217-0369-CD41-B32D-928B917ABD56}" name="Raw_Review_Text" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{655630C9-6872-2648-B4C4-EF46DC8C63FC}" name="Theme" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{83274B5D-B1A2-9C43-83B1-217689641447}" name="Sub_Theme" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{5012791F-CC7B-A14E-B6F8-C210EEA0E819}" name="Churn_Signal" dataDxfId="8"/>
-    <tableColumn id="19" xr3:uid="{62935A5E-A60E-0B48-82CA-010C5F46E946}" name="Churn_Flag" dataDxfId="7">
-      <calculatedColumnFormula>IF(F2="yes",1,0)</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{D8B7633B-220A-7845-A647-D85993E95A37}" name="Review_Id" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{19086F0C-CE61-CC49-8DCF-68D95499EB1C}" name="Source" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{93741217-0369-CD41-B32D-928B917ABD56}" name="Raw_Review_Text" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{655630C9-6872-2648-B4C4-EF46DC8C63FC}" name="Theme" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{83274B5D-B1A2-9C43-83B1-217689641447}" name="Sub_Theme" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{5012791F-CC7B-A14E-B6F8-C210EEA0E819}" name="Churn_Signal" dataDxfId="6"/>
+    <tableColumn id="19" xr3:uid="{62935A5E-A60E-0B48-82CA-010C5F46E946}" name="Churn_Flag" dataDxfId="5">
+      <calculatedColumnFormula>IF(F4="yes",1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B4E101EC-A34B-CD4A-A1D9-FDE5F14F1FDE}" name="Req_Group" dataDxfId="6">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(D2&amp;"-"&amp;E2,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</calculatedColumnFormula>
+    <tableColumn id="8" xr3:uid="{B4E101EC-A34B-CD4A-A1D9-FDE5F14F1FDE}" name="Req_Group" dataDxfId="4">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(D4&amp;"-"&amp;E4,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{340D3186-319B-9E4A-84B9-ABD58EF87C52}" name="Req_ID" dataDxfId="5">
-      <calculatedColumnFormula>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D2&amp;"-"&amp;E2,Analysis_Lookups!$C$3:$C$13,0)),"Future")</calculatedColumnFormula>
+    <tableColumn id="9" xr3:uid="{340D3186-319B-9E4A-84B9-ABD58EF87C52}" name="Req_ID" dataDxfId="3">
+      <calculatedColumnFormula>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D4&amp;"-"&amp;E4,Analysis_Lookups!$C$3:$C$13,0)),"Future")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{7BF352CD-BF3A-4E4A-B382-313CC620984A}" name="Cluster_ID" dataDxfId="4">
-      <calculatedColumnFormula>D2&amp;"-"&amp;E2&amp;"-"&amp;COUNTIFS($D$2:D2,D2,$E$2:E2,E2)</calculatedColumnFormula>
+    <tableColumn id="11" xr3:uid="{7BF352CD-BF3A-4E4A-B382-313CC620984A}" name="Cluster_ID" dataDxfId="2">
+      <calculatedColumnFormula>D4&amp;"-"&amp;E4&amp;"-"&amp;COUNTIFS($D$4:D4,D4,$E$4:E4,E4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{D6984204-8DF0-E74A-B5F0-AC89A2DE0C93}" name="Frequency" dataDxfId="3">
-      <calculatedColumnFormula>COUNTIFS($D$2:$D$225,D2,$E$2:$E$225,E2)</calculatedColumnFormula>
+    <tableColumn id="12" xr3:uid="{D6984204-8DF0-E74A-B5F0-AC89A2DE0C93}" name="Frequency" dataDxfId="1">
+      <calculatedColumnFormula>COUNTIFS($D$4:$D$227,D4,$E$4:$E$227,E4)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Affinity Analysis Table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -9551,7 +9564,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{8BCD8680-DD18-9346-8156-4576C2AEE536}" name="Table2479" displayName="Table2479" ref="C9:E15" totalsRowShown="0" headerRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{8BCD8680-DD18-9346-8156-4576C2AEE536}" name="Table2479" displayName="Table2479" ref="C9:E15" totalsRowShown="0" headerRowDxfId="15">
   <autoFilter ref="C9:E15" xr:uid="{8BCD8680-DD18-9346-8156-4576C2AEE536}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{DCBD08E8-6984-5C42-B9B7-1AB529872030}" name="Theme-Sub_Theme"/>
@@ -9563,7 +9576,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{EDB269F5-078B-6748-A0EC-C7DF18A8232A}" name="Table5810" displayName="Table5810" ref="H9:J13" totalsRowShown="0" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{EDB269F5-078B-6748-A0EC-C7DF18A8232A}" name="Table5810" displayName="Table5810" ref="H9:J13" totalsRowShown="0" headerRowDxfId="14">
   <autoFilter ref="H9:J13" xr:uid="{EDB269F5-078B-6748-A0EC-C7DF18A8232A}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{4684E164-14A9-834A-949B-A280DB0A5DE3}" name="ReqGroup"/>
@@ -9891,7 +9904,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8EC9903-33F8-E045-9CC2-C219EFC04054}">
-  <dimension ref="A1:V226"/>
+  <dimension ref="A1:V228"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="20.83203125" customWidth="1"/>
@@ -9908,215 +9921,155 @@
     <col min="22" max="22" width="21.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:22" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="28" t="s">
+        <v>321</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+    </row>
+    <row r="2" spans="1:22" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="31"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+    </row>
+    <row r="3" spans="1:22" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G3" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="24"/>
-      <c r="T1" s="24"/>
-      <c r="U1" s="24"/>
-      <c r="V1" s="24"/>
-    </row>
-    <row r="2" spans="1:22" ht="90" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="S3" s="24"/>
+      <c r="T3" s="24"/>
+      <c r="U3" s="24"/>
+      <c r="V3" s="24"/>
+    </row>
+    <row r="4" spans="1:22" ht="90" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="G2">
-        <f t="shared" ref="G2:G33" si="0">IF(F2="yes",1,0)</f>
+      <c r="G4">
+        <f t="shared" ref="G4:G35" si="0">IF(F4="yes",1,0)</f>
         <v>0</v>
       </c>
-      <c r="H2" s="3" t="str">
-        <f>IFERROR(VLOOKUP(D2&amp;"-"&amp;E2,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
+      <c r="H4" s="3" t="str">
+        <f>IFERROR(VLOOKUP(D4&amp;"-"&amp;E4,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
         <v>Reliable Sync</v>
       </c>
-      <c r="I2" s="3" t="str">
-        <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D2&amp;"-"&amp;E2,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
+      <c r="I4" s="3" t="str">
+        <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D4&amp;"-"&amp;E4,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
         <v>FR-04</v>
       </c>
-      <c r="J2" s="4" t="str">
-        <f>D2&amp;"-"&amp;E2&amp;"-"&amp;COUNTIFS($D$2:D2,D2,$E$2:E2,E2)</f>
+      <c r="J4" s="4" t="str">
+        <f>D4&amp;"-"&amp;E4&amp;"-"&amp;COUNTIFS($D$4:D4,D4,$E$4:E4,E4)</f>
         <v>Bug-Tasks-1</v>
       </c>
-      <c r="K2" s="3">
-        <f>COUNTIFS($D$2:$D$225,D2,$E$2:$E$225,E2)</f>
+      <c r="K4" s="3">
+        <f>COUNTIFS($D$4:$D$227,D4,$E$4:$E$227,E4)</f>
         <v>2</v>
       </c>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="22"/>
-    </row>
-    <row r="3" spans="1:22" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="S4" s="22"/>
+      <c r="T4" s="22"/>
+      <c r="U4" s="22"/>
+      <c r="V4" s="22"/>
+    </row>
+    <row r="5" spans="1:22" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="G3">
+      <c r="G5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H3" s="1" t="str">
-        <f>IFERROR(VLOOKUP(D3&amp;"-"&amp;E3,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Reliable Sync</v>
-      </c>
-      <c r="I3" s="1" t="str">
-        <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D3&amp;"-"&amp;E3,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-04</v>
-      </c>
-      <c r="J3" s="4" t="str">
-        <f>D3&amp;"-"&amp;E3&amp;"-"&amp;COUNTIFS($D$2:D3,D3,$E$2:E3,E3)</f>
-        <v>Bug-Calendar-1</v>
-      </c>
-      <c r="K3" s="1">
-        <f>COUNTIFS($D$2:$D$225,D3,$E$2:$E$225,E3)</f>
-        <v>9</v>
-      </c>
-      <c r="S3" s="23"/>
-      <c r="T3" s="23"/>
-      <c r="U3" s="23"/>
-      <c r="V3" s="23"/>
-    </row>
-    <row r="4" spans="1:22" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="G4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H4" s="1" t="str">
-        <f>IFERROR(VLOOKUP(D4&amp;"-"&amp;E4,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Reliable Sync</v>
-      </c>
-      <c r="I4" s="1" t="str">
-        <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D4&amp;"-"&amp;E4,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-04</v>
-      </c>
-      <c r="J4" s="4" t="str">
-        <f>D4&amp;"-"&amp;E4&amp;"-"&amp;COUNTIFS($D$2:D4,D4,$E$2:E4,E4)</f>
-        <v>Bug-UI-1</v>
-      </c>
-      <c r="K4" s="1">
-        <f t="shared" ref="K4:K35" si="1">COUNTIFS($D$2:$D$225,D4,$E$2:$E$225,E4)</f>
-        <v>7</v>
-      </c>
-      <c r="S4" s="23"/>
-      <c r="T4" s="23"/>
-      <c r="U4" s="23"/>
-      <c r="V4" s="23"/>
-    </row>
-    <row r="5" spans="1:22" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="H5" s="1" t="str">
         <f>IFERROR(VLOOKUP(D5&amp;"-"&amp;E5,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Pricing &amp; Paywall</v>
+        <v>Reliable Sync</v>
       </c>
       <c r="I5" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D5&amp;"-"&amp;E5,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>Future</v>
+        <v>FR-04</v>
       </c>
       <c r="J5" s="4" t="str">
-        <f>D5&amp;"-"&amp;E5&amp;"-"&amp;COUNTIFS($D$2:D5,D5,$E$2:E5,E5)</f>
-        <v>Subscription-Refund-1</v>
+        <f>D5&amp;"-"&amp;E5&amp;"-"&amp;COUNTIFS($D$4:D5,D5,$E$4:E5,E5)</f>
+        <v>Bug-Calendar-1</v>
       </c>
       <c r="K5" s="1">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <f>COUNTIFS($D$4:$D$227,D5,$E$4:$E$227,E5)</f>
+        <v>9</v>
       </c>
       <c r="S5" s="23"/>
       <c r="T5" s="23"/>
@@ -10125,19 +10078,19 @@
     </row>
     <row r="6" spans="1:22" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>240</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>257</v>
@@ -10148,19 +10101,19 @@
       </c>
       <c r="H6" s="1" t="str">
         <f>IFERROR(VLOOKUP(D6&amp;"-"&amp;E6,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Setup Efficiency</v>
+        <v>Reliable Sync</v>
       </c>
       <c r="I6" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D6&amp;"-"&amp;E6,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>SR-03</v>
+        <v>FR-04</v>
       </c>
       <c r="J6" s="4" t="str">
-        <f>D6&amp;"-"&amp;E6&amp;"-"&amp;COUNTIFS($D$2:D6,D6,$E$2:E6,E6)</f>
-        <v>UI-Clutter-1</v>
+        <f>D6&amp;"-"&amp;E6&amp;"-"&amp;COUNTIFS($D$4:D6,D6,$E$4:E6,E6)</f>
+        <v>Bug-UI-1</v>
       </c>
       <c r="K6" s="1">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <f t="shared" ref="K6:K37" si="1">COUNTIFS($D$4:$D$227,D6,$E$4:$E$227,E6)</f>
+        <v>7</v>
       </c>
       <c r="S6" s="23"/>
       <c r="T6" s="23"/>
@@ -10169,42 +10122,42 @@
     </row>
     <row r="7" spans="1:22" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="1" t="str">
         <f>IFERROR(VLOOKUP(D7&amp;"-"&amp;E7,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Support &amp; UX</v>
+        <v>Pricing &amp; Paywall</v>
       </c>
       <c r="I7" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D7&amp;"-"&amp;E7,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
         <v>Future</v>
       </c>
       <c r="J7" s="4" t="str">
-        <f>D7&amp;"-"&amp;E7&amp;"-"&amp;COUNTIFS($D$2:D7,D7,$E$2:E7,E7)</f>
-        <v>Other-Uncategorized-1</v>
+        <f>D7&amp;"-"&amp;E7&amp;"-"&amp;COUNTIFS($D$4:D7,D7,$E$4:E7,E7)</f>
+        <v>Subscription-Refund-1</v>
       </c>
       <c r="K7" s="1">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S7" s="23"/>
       <c r="T7" s="23"/>
@@ -10213,42 +10166,42 @@
     </row>
     <row r="8" spans="1:22" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="1" t="str">
         <f>IFERROR(VLOOKUP(D8&amp;"-"&amp;E8,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Pricing &amp; Paywall</v>
+        <v>Setup Efficiency</v>
       </c>
       <c r="I8" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D8&amp;"-"&amp;E8,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>Future</v>
+        <v>SR-03</v>
       </c>
       <c r="J8" s="4" t="str">
-        <f>D8&amp;"-"&amp;E8&amp;"-"&amp;COUNTIFS($D$2:D8,D8,$E$2:E8,E8)</f>
-        <v>Subscription-Paywall-1</v>
+        <f>D8&amp;"-"&amp;E8&amp;"-"&amp;COUNTIFS($D$4:D8,D8,$E$4:E8,E8)</f>
+        <v>UI-Clutter-1</v>
       </c>
       <c r="K8" s="1">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S8" s="23"/>
       <c r="T8" s="23"/>
@@ -10257,42 +10210,42 @@
     </row>
     <row r="9" spans="1:22" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="1" t="str">
         <f>IFERROR(VLOOKUP(D9&amp;"-"&amp;E9,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Setup Efficiency</v>
+        <v>Support &amp; UX</v>
       </c>
       <c r="I9" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D9&amp;"-"&amp;E9,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>SR-01</v>
+        <v>Future</v>
       </c>
       <c r="J9" s="4" t="str">
-        <f>D9&amp;"-"&amp;E9&amp;"-"&amp;COUNTIFS($D$2:D9,D9,$E$2:E9,E9)</f>
-        <v>UI-Setup-1</v>
+        <f>D9&amp;"-"&amp;E9&amp;"-"&amp;COUNTIFS($D$4:D9,D9,$E$4:E9,E9)</f>
+        <v>Other-Uncategorized-1</v>
       </c>
       <c r="K9" s="1">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="S9" s="23"/>
       <c r="T9" s="23"/>
@@ -10301,13 +10254,13 @@
     </row>
     <row r="10" spans="1:22" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>9</v>
@@ -10316,11 +10269,11 @@
         <v>242</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="1" t="str">
         <f>IFERROR(VLOOKUP(D10&amp;"-"&amp;E10,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
@@ -10331,8 +10284,8 @@
         <v>Future</v>
       </c>
       <c r="J10" s="4" t="str">
-        <f>D10&amp;"-"&amp;E10&amp;"-"&amp;COUNTIFS($D$2:D10,D10,$E$2:E10,E10)</f>
-        <v>Subscription-Paywall-2</v>
+        <f>D10&amp;"-"&amp;E10&amp;"-"&amp;COUNTIFS($D$4:D10,D10,$E$4:E10,E10)</f>
+        <v>Subscription-Paywall-1</v>
       </c>
       <c r="K10" s="1">
         <f t="shared" si="1"/>
@@ -10345,42 +10298,42 @@
     </row>
     <row r="11" spans="1:22" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="1" t="str">
         <f>IFERROR(VLOOKUP(D11&amp;"-"&amp;E11,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Crash Prevention</v>
+        <v>Setup Efficiency</v>
       </c>
       <c r="I11" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D11&amp;"-"&amp;E11,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>NFR-03</v>
+        <v>SR-01</v>
       </c>
       <c r="J11" s="4" t="str">
-        <f>D11&amp;"-"&amp;E11&amp;"-"&amp;COUNTIFS($D$2:D11,D11,$E$2:E11,E11)</f>
-        <v>Performance-Crash-1</v>
+        <f>D11&amp;"-"&amp;E11&amp;"-"&amp;COUNTIFS($D$4:D11,D11,$E$4:E11,E11)</f>
+        <v>UI-Setup-1</v>
       </c>
       <c r="K11" s="1">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S11" s="23"/>
       <c r="T11" s="23"/>
@@ -10389,42 +10342,42 @@
     </row>
     <row r="12" spans="1:22" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G12">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1" t="str">
         <f>IFERROR(VLOOKUP(D12&amp;"-"&amp;E12,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Reliable Sync</v>
+        <v>Pricing &amp; Paywall</v>
       </c>
       <c r="I12" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D12&amp;"-"&amp;E12,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-04</v>
+        <v>Future</v>
       </c>
       <c r="J12" s="4" t="str">
-        <f>D12&amp;"-"&amp;E12&amp;"-"&amp;COUNTIFS($D$2:D12,D12,$E$2:E12,E12)</f>
-        <v>Bug-Tasks-2</v>
+        <f>D12&amp;"-"&amp;E12&amp;"-"&amp;COUNTIFS($D$4:D12,D12,$E$4:E12,E12)</f>
+        <v>Subscription-Paywall-2</v>
       </c>
       <c r="K12" s="1">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="S12" s="23"/>
       <c r="T12" s="23"/>
@@ -10433,42 +10386,42 @@
     </row>
     <row r="13" spans="1:22" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="1" t="str">
         <f>IFERROR(VLOOKUP(D13&amp;"-"&amp;E13,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Pricing &amp; Paywall</v>
+        <v>Crash Prevention</v>
       </c>
       <c r="I13" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D13&amp;"-"&amp;E13,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>Future</v>
+        <v>NFR-03</v>
       </c>
       <c r="J13" s="4" t="str">
-        <f>D13&amp;"-"&amp;E13&amp;"-"&amp;COUNTIFS($D$2:D13,D13,$E$2:E13,E13)</f>
-        <v>Subscription-Paywall-3</v>
+        <f>D13&amp;"-"&amp;E13&amp;"-"&amp;COUNTIFS($D$4:D13,D13,$E$4:E13,E13)</f>
+        <v>Performance-Crash-1</v>
       </c>
       <c r="K13" s="1">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S13" s="23"/>
       <c r="T13" s="23"/>
@@ -10477,59 +10430,63 @@
     </row>
     <row r="14" spans="1:22" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="1" t="str">
         <f>IFERROR(VLOOKUP(D14&amp;"-"&amp;E14,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Routine Engine</v>
+        <v>Reliable Sync</v>
       </c>
       <c r="I14" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D14&amp;"-"&amp;E14,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-04</v>
       </c>
       <c r="J14" s="4" t="str">
-        <f>D14&amp;"-"&amp;E14&amp;"-"&amp;COUNTIFS($D$2:D14,D14,$E$2:E14,E14)</f>
-        <v>Feature_Request-Routines-1</v>
+        <f>D14&amp;"-"&amp;E14&amp;"-"&amp;COUNTIFS($D$4:D14,D14,$E$4:E14,E14)</f>
+        <v>Bug-Tasks-2</v>
       </c>
       <c r="K14" s="1">
         <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="S14" s="23"/>
+      <c r="T14" s="23"/>
+      <c r="U14" s="23"/>
+      <c r="V14" s="23"/>
     </row>
     <row r="15" spans="1:22" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>258</v>
@@ -10540,123 +10497,127 @@
       </c>
       <c r="H15" s="1" t="str">
         <f>IFERROR(VLOOKUP(D15&amp;"-"&amp;E15,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Routine Engine</v>
+        <v>Pricing &amp; Paywall</v>
       </c>
       <c r="I15" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D15&amp;"-"&amp;E15,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>Future</v>
       </c>
       <c r="J15" s="4" t="str">
-        <f>D15&amp;"-"&amp;E15&amp;"-"&amp;COUNTIFS($D$2:D15,D15,$E$2:E15,E15)</f>
-        <v>Feature_Request-Routines-2</v>
+        <f>D15&amp;"-"&amp;E15&amp;"-"&amp;COUNTIFS($D$4:D15,D15,$E$4:E15,E15)</f>
+        <v>Subscription-Paywall-3</v>
       </c>
       <c r="K15" s="1">
         <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23"/>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
     </row>
     <row r="16" spans="1:22" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G16">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="1" t="str">
         <f>IFERROR(VLOOKUP(D16&amp;"-"&amp;E16,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Support &amp; UX</v>
+        <v>Routine Engine</v>
       </c>
       <c r="I16" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D16&amp;"-"&amp;E16,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>Future</v>
+        <v>FR-01</v>
       </c>
       <c r="J16" s="4" t="str">
-        <f>D16&amp;"-"&amp;E16&amp;"-"&amp;COUNTIFS($D$2:D16,D16,$E$2:E16,E16)</f>
-        <v>Other-Uncategorized-2</v>
+        <f>D16&amp;"-"&amp;E16&amp;"-"&amp;COUNTIFS($D$4:D16,D16,$E$4:E16,E16)</f>
+        <v>Feature_Request-Routines-1</v>
       </c>
       <c r="K16" s="1">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="1" t="str">
         <f>IFERROR(VLOOKUP(D17&amp;"-"&amp;E17,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Support &amp; UX</v>
+        <v>Routine Engine</v>
       </c>
       <c r="I17" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D17&amp;"-"&amp;E17,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>Future</v>
+        <v>FR-01</v>
       </c>
       <c r="J17" s="4" t="str">
-        <f>D17&amp;"-"&amp;E17&amp;"-"&amp;COUNTIFS($D$2:D17,D17,$E$2:E17,E17)</f>
-        <v>Other-Uncategorized-3</v>
+        <f>D17&amp;"-"&amp;E17&amp;"-"&amp;COUNTIFS($D$4:D17,D17,$E$4:E17,E17)</f>
+        <v>Feature_Request-Routines-2</v>
       </c>
       <c r="K17" s="1">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>241</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="1" t="str">
         <f>IFERROR(VLOOKUP(D18&amp;"-"&amp;E18,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
@@ -10667,29 +10628,29 @@
         <v>Future</v>
       </c>
       <c r="J18" s="4" t="str">
-        <f>D18&amp;"-"&amp;E18&amp;"-"&amp;COUNTIFS($D$2:D18,D18,$E$2:E18,E18)</f>
-        <v>UI-Uncategorized-1</v>
+        <f>D18&amp;"-"&amp;E18&amp;"-"&amp;COUNTIFS($D$4:D18,D18,$E$4:E18,E18)</f>
+        <v>Other-Uncategorized-2</v>
       </c>
       <c r="K18" s="1">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>257</v>
@@ -10700,15 +10661,15 @@
       </c>
       <c r="H19" s="1" t="str">
         <f>IFERROR(VLOOKUP(D19&amp;"-"&amp;E19,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Pricing &amp; Paywall</v>
+        <v>Support &amp; UX</v>
       </c>
       <c r="I19" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D19&amp;"-"&amp;E19,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
         <v>Future</v>
       </c>
       <c r="J19" s="4" t="str">
-        <f>D19&amp;"-"&amp;E19&amp;"-"&amp;COUNTIFS($D$2:D19,D19,$E$2:E19,E19)</f>
-        <v>Subscription-Paywall-4</v>
+        <f>D19&amp;"-"&amp;E19&amp;"-"&amp;COUNTIFS($D$4:D19,D19,$E$4:E19,E19)</f>
+        <v>Other-Uncategorized-3</v>
       </c>
       <c r="K19" s="1">
         <f t="shared" si="1"/>
@@ -10717,38 +10678,38 @@
     </row>
     <row r="20" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G20">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" s="1" t="str">
         <f>IFERROR(VLOOKUP(D20&amp;"-"&amp;E20,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Setup Efficiency</v>
+        <v>Support &amp; UX</v>
       </c>
       <c r="I20" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D20&amp;"-"&amp;E20,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>SR-03</v>
+        <v>Future</v>
       </c>
       <c r="J20" s="4" t="str">
-        <f>D20&amp;"-"&amp;E20&amp;"-"&amp;COUNTIFS($D$2:D20,D20,$E$2:E20,E20)</f>
-        <v>UI-Clutter-2</v>
+        <f>D20&amp;"-"&amp;E20&amp;"-"&amp;COUNTIFS($D$4:D20,D20,$E$4:E20,E20)</f>
+        <v>UI-Uncategorized-1</v>
       </c>
       <c r="K20" s="1">
         <f t="shared" si="1"/>
@@ -10757,19 +10718,19 @@
     </row>
     <row r="21" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>257</v>
@@ -10780,76 +10741,76 @@
       </c>
       <c r="H21" s="1" t="str">
         <f>IFERROR(VLOOKUP(D21&amp;"-"&amp;E21,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Setup Efficiency</v>
+        <v>Pricing &amp; Paywall</v>
       </c>
       <c r="I21" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D21&amp;"-"&amp;E21,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>SR-01</v>
+        <v>Future</v>
       </c>
       <c r="J21" s="4" t="str">
-        <f>D21&amp;"-"&amp;E21&amp;"-"&amp;COUNTIFS($D$2:D21,D21,$E$2:E21,E21)</f>
-        <v>UI-Setup-2</v>
+        <f>D21&amp;"-"&amp;E21&amp;"-"&amp;COUNTIFS($D$4:D21,D21,$E$4:E21,E21)</f>
+        <v>Subscription-Paywall-4</v>
       </c>
       <c r="K21" s="1">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G22">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="1" t="str">
         <f>IFERROR(VLOOKUP(D22&amp;"-"&amp;E22,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Routine Engine</v>
+        <v>Setup Efficiency</v>
       </c>
       <c r="I22" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D22&amp;"-"&amp;E22,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>SR-03</v>
       </c>
       <c r="J22" s="4" t="str">
-        <f>D22&amp;"-"&amp;E22&amp;"-"&amp;COUNTIFS($D$2:D22,D22,$E$2:E22,E22)</f>
-        <v>Feature_Request-Routines-3</v>
+        <f>D22&amp;"-"&amp;E22&amp;"-"&amp;COUNTIFS($D$4:D22,D22,$E$4:E22,E22)</f>
+        <v>UI-Clutter-2</v>
       </c>
       <c r="K22" s="1">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>257</v>
@@ -10860,36 +10821,36 @@
       </c>
       <c r="H23" s="1" t="str">
         <f>IFERROR(VLOOKUP(D23&amp;"-"&amp;E23,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Routine Engine</v>
+        <v>Setup Efficiency</v>
       </c>
       <c r="I23" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D23&amp;"-"&amp;E23,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>SR-01</v>
       </c>
       <c r="J23" s="4" t="str">
-        <f>D23&amp;"-"&amp;E23&amp;"-"&amp;COUNTIFS($D$2:D23,D23,$E$2:E23,E23)</f>
-        <v>Feature_Request-Routines-4</v>
+        <f>D23&amp;"-"&amp;E23&amp;"-"&amp;COUNTIFS($D$4:D23,D23,$E$4:E23,E23)</f>
+        <v>UI-Setup-2</v>
       </c>
       <c r="K23" s="1">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>257</v>
@@ -10900,30 +10861,30 @@
       </c>
       <c r="H24" s="1" t="str">
         <f>IFERROR(VLOOKUP(D24&amp;"-"&amp;E24,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Support &amp; UX</v>
+        <v>Routine Engine</v>
       </c>
       <c r="I24" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D24&amp;"-"&amp;E24,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>Future</v>
+        <v>FR-01</v>
       </c>
       <c r="J24" s="4" t="str">
-        <f>D24&amp;"-"&amp;E24&amp;"-"&amp;COUNTIFS($D$2:D24,D24,$E$2:E24,E24)</f>
-        <v>Subscription-Auto_Renew_Charge-1</v>
+        <f>D24&amp;"-"&amp;E24&amp;"-"&amp;COUNTIFS($D$4:D24,D24,$E$4:E24,E24)</f>
+        <v>Feature_Request-Routines-3</v>
       </c>
       <c r="K24" s="1">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>7</v>
@@ -10932,11 +10893,11 @@
         <v>245</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G25">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="1" t="str">
         <f>IFERROR(VLOOKUP(D25&amp;"-"&amp;E25,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
@@ -10947,8 +10908,8 @@
         <v>FR-01</v>
       </c>
       <c r="J25" s="4" t="str">
-        <f>D25&amp;"-"&amp;E25&amp;"-"&amp;COUNTIFS($D$2:D25,D25,$E$2:E25,E25)</f>
-        <v>Feature_Request-Routines-5</v>
+        <f>D25&amp;"-"&amp;E25&amp;"-"&amp;COUNTIFS($D$4:D25,D25,$E$4:E25,E25)</f>
+        <v>Feature_Request-Routines-4</v>
       </c>
       <c r="K25" s="1">
         <f t="shared" si="1"/>
@@ -10957,19 +10918,19 @@
     </row>
     <row r="26" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>257</v>
@@ -10980,36 +10941,36 @@
       </c>
       <c r="H26" s="1" t="str">
         <f>IFERROR(VLOOKUP(D26&amp;"-"&amp;E26,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Routine Engine</v>
+        <v>Support &amp; UX</v>
       </c>
       <c r="I26" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D26&amp;"-"&amp;E26,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>Future</v>
       </c>
       <c r="J26" s="4" t="str">
-        <f>D26&amp;"-"&amp;E26&amp;"-"&amp;COUNTIFS($D$2:D26,D26,$E$2:E26,E26)</f>
-        <v>Feature_Request-Routines-6</v>
+        <f>D26&amp;"-"&amp;E26&amp;"-"&amp;COUNTIFS($D$4:D26,D26,$E$4:E26,E26)</f>
+        <v>Subscription-Auto_Renew_Charge-1</v>
       </c>
       <c r="K26" s="1">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>258</v>
@@ -11020,30 +10981,30 @@
       </c>
       <c r="H27" s="1" t="str">
         <f>IFERROR(VLOOKUP(D27&amp;"-"&amp;E27,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Pricing &amp; Paywall</v>
+        <v>Routine Engine</v>
       </c>
       <c r="I27" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D27&amp;"-"&amp;E27,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>Future</v>
+        <v>FR-01</v>
       </c>
       <c r="J27" s="4" t="str">
-        <f>D27&amp;"-"&amp;E27&amp;"-"&amp;COUNTIFS($D$2:D27,D27,$E$2:E27,E27)</f>
-        <v>Subscription-Refund-2</v>
+        <f>D27&amp;"-"&amp;E27&amp;"-"&amp;COUNTIFS($D$4:D27,D27,$E$4:E27,E27)</f>
+        <v>Feature_Request-Routines-5</v>
       </c>
       <c r="K27" s="1">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>7</v>
@@ -11067,8 +11028,8 @@
         <v>FR-01</v>
       </c>
       <c r="J28" s="4" t="str">
-        <f>D28&amp;"-"&amp;E28&amp;"-"&amp;COUNTIFS($D$2:D28,D28,$E$2:E28,E28)</f>
-        <v>Feature_Request-Routines-7</v>
+        <f>D28&amp;"-"&amp;E28&amp;"-"&amp;COUNTIFS($D$4:D28,D28,$E$4:E28,E28)</f>
+        <v>Feature_Request-Routines-6</v>
       </c>
       <c r="K28" s="1">
         <f t="shared" si="1"/>
@@ -11077,59 +11038,59 @@
     </row>
     <row r="29" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G29">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="1" t="str">
         <f>IFERROR(VLOOKUP(D29&amp;"-"&amp;E29,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Routine Engine</v>
+        <v>Pricing &amp; Paywall</v>
       </c>
       <c r="I29" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D29&amp;"-"&amp;E29,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>Future</v>
       </c>
       <c r="J29" s="4" t="str">
-        <f>D29&amp;"-"&amp;E29&amp;"-"&amp;COUNTIFS($D$2:D29,D29,$E$2:E29,E29)</f>
-        <v>Feature_Request-Routines-8</v>
+        <f>D29&amp;"-"&amp;E29&amp;"-"&amp;COUNTIFS($D$4:D29,D29,$E$4:E29,E29)</f>
+        <v>Subscription-Refund-2</v>
       </c>
       <c r="K29" s="1">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>8</v>
+        <v>245</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>257</v>
@@ -11140,36 +11101,36 @@
       </c>
       <c r="H30" s="1" t="str">
         <f>IFERROR(VLOOKUP(D30&amp;"-"&amp;E30,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Reliable Sync</v>
+        <v>Routine Engine</v>
       </c>
       <c r="I30" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D30&amp;"-"&amp;E30,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-04</v>
+        <v>FR-01</v>
       </c>
       <c r="J30" s="4" t="str">
-        <f>D30&amp;"-"&amp;E30&amp;"-"&amp;COUNTIFS($D$2:D30,D30,$E$2:E30,E30)</f>
-        <v>Bug-UI-2</v>
+        <f>D30&amp;"-"&amp;E30&amp;"-"&amp;COUNTIFS($D$4:D30,D30,$E$4:E30,E30)</f>
+        <v>Feature_Request-Routines-7</v>
       </c>
       <c r="K30" s="1">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>8</v>
+        <v>245</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>257</v>
@@ -11180,236 +11141,236 @@
       </c>
       <c r="H31" s="1" t="str">
         <f>IFERROR(VLOOKUP(D31&amp;"-"&amp;E31,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Reliable Sync</v>
+        <v>Routine Engine</v>
       </c>
       <c r="I31" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D31&amp;"-"&amp;E31,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-04</v>
+        <v>FR-01</v>
       </c>
       <c r="J31" s="4" t="str">
-        <f>D31&amp;"-"&amp;E31&amp;"-"&amp;COUNTIFS($D$2:D31,D31,$E$2:E31,E31)</f>
-        <v>Bug-UI-3</v>
+        <f>D31&amp;"-"&amp;E31&amp;"-"&amp;COUNTIFS($D$4:D31,D31,$E$4:E31,E31)</f>
+        <v>Feature_Request-Routines-8</v>
       </c>
       <c r="K31" s="1">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>244</v>
+        <v>8</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G32">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" s="1" t="str">
         <f>IFERROR(VLOOKUP(D32&amp;"-"&amp;E32,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Crash Prevention</v>
+        <v>Reliable Sync</v>
       </c>
       <c r="I32" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D32&amp;"-"&amp;E32,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>NFR-03</v>
+        <v>FR-04</v>
       </c>
       <c r="J32" s="4" t="str">
-        <f>D32&amp;"-"&amp;E32&amp;"-"&amp;COUNTIFS($D$2:D32,D32,$E$2:E32,E32)</f>
-        <v>Performance-Crash-2</v>
+        <f>D32&amp;"-"&amp;E32&amp;"-"&amp;COUNTIFS($D$4:D32,D32,$E$4:E32,E32)</f>
+        <v>Bug-UI-2</v>
       </c>
       <c r="K32" s="1">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="4" t="s">
-        <v>241</v>
-      </c>
       <c r="F33" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="1" t="str">
         <f>IFERROR(VLOOKUP(D33&amp;"-"&amp;E33,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Support &amp; UX</v>
+        <v>Reliable Sync</v>
       </c>
       <c r="I33" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D33&amp;"-"&amp;E33,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>Future</v>
+        <v>FR-04</v>
       </c>
       <c r="J33" s="4" t="str">
-        <f>D33&amp;"-"&amp;E33&amp;"-"&amp;COUNTIFS($D$2:D33,D33,$E$2:E33,E33)</f>
-        <v>UI-Uncategorized-2</v>
+        <f>D33&amp;"-"&amp;E33&amp;"-"&amp;COUNTIFS($D$4:D33,D33,$E$4:E33,E33)</f>
+        <v>Bug-UI-3</v>
       </c>
       <c r="K33" s="1">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>258</v>
       </c>
       <c r="G34">
-        <f t="shared" ref="G34:G65" si="2">IF(F34="yes",1,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H34" s="1" t="str">
         <f>IFERROR(VLOOKUP(D34&amp;"-"&amp;E34,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Support &amp; UX</v>
+        <v>Crash Prevention</v>
       </c>
       <c r="I34" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D34&amp;"-"&amp;E34,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>Future</v>
+        <v>NFR-03</v>
       </c>
       <c r="J34" s="4" t="str">
-        <f>D34&amp;"-"&amp;E34&amp;"-"&amp;COUNTIFS($D$2:D34,D34,$E$2:E34,E34)</f>
-        <v>UI-Uncategorized-3</v>
+        <f>D34&amp;"-"&amp;E34&amp;"-"&amp;COUNTIFS($D$4:D34,D34,$E$4:E34,E34)</f>
+        <v>Performance-Crash-2</v>
       </c>
       <c r="K34" s="1">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>258</v>
       </c>
       <c r="G35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H35" s="1" t="str">
         <f>IFERROR(VLOOKUP(D35&amp;"-"&amp;E35,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Pricing &amp; Paywall</v>
+        <v>Support &amp; UX</v>
       </c>
       <c r="I35" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D35&amp;"-"&amp;E35,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
         <v>Future</v>
       </c>
       <c r="J35" s="4" t="str">
-        <f>D35&amp;"-"&amp;E35&amp;"-"&amp;COUNTIFS($D$2:D35,D35,$E$2:E35,E35)</f>
-        <v>Subscription-Paywall-5</v>
+        <f>D35&amp;"-"&amp;E35&amp;"-"&amp;COUNTIFS($D$4:D35,D35,$E$4:E35,E35)</f>
+        <v>UI-Uncategorized-2</v>
       </c>
       <c r="K35" s="1">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>258</v>
       </c>
       <c r="G36">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="G36:G67" si="2">IF(F36="yes",1,0)</f>
         <v>1</v>
       </c>
       <c r="H36" s="1" t="str">
         <f>IFERROR(VLOOKUP(D36&amp;"-"&amp;E36,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Pricing &amp; Paywall</v>
+        <v>Support &amp; UX</v>
       </c>
       <c r="I36" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D36&amp;"-"&amp;E36,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
         <v>Future</v>
       </c>
       <c r="J36" s="4" t="str">
-        <f>D36&amp;"-"&amp;E36&amp;"-"&amp;COUNTIFS($D$2:D36,D36,$E$2:E36,E36)</f>
-        <v>Subscription-Paywall-6</v>
+        <f>D36&amp;"-"&amp;E36&amp;"-"&amp;COUNTIFS($D$4:D36,D36,$E$4:E36,E36)</f>
+        <v>UI-Uncategorized-3</v>
       </c>
       <c r="K36" s="1">
-        <f t="shared" ref="K36:K67" si="3">COUNTIFS($D$2:$D$225,D36,$E$2:$E$225,E36)</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>258</v>
@@ -11420,76 +11381,76 @@
       </c>
       <c r="H37" s="1" t="str">
         <f>IFERROR(VLOOKUP(D37&amp;"-"&amp;E37,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Support &amp; UX</v>
+        <v>Pricing &amp; Paywall</v>
       </c>
       <c r="I37" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D37&amp;"-"&amp;E37,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
         <v>Future</v>
       </c>
       <c r="J37" s="4" t="str">
-        <f>D37&amp;"-"&amp;E37&amp;"-"&amp;COUNTIFS($D$2:D37,D37,$E$2:E37,E37)</f>
-        <v>Bug-Uncategorized-1</v>
+        <f>D37&amp;"-"&amp;E37&amp;"-"&amp;COUNTIFS($D$4:D37,D37,$E$4:E37,E37)</f>
+        <v>Subscription-Paywall-5</v>
       </c>
       <c r="K37" s="1">
-        <f t="shared" si="3"/>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G38">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="1" t="str">
         <f>IFERROR(VLOOKUP(D38&amp;"-"&amp;E38,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Setup Efficiency</v>
+        <v>Pricing &amp; Paywall</v>
       </c>
       <c r="I38" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D38&amp;"-"&amp;E38,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>SR-03</v>
+        <v>Future</v>
       </c>
       <c r="J38" s="4" t="str">
-        <f>D38&amp;"-"&amp;E38&amp;"-"&amp;COUNTIFS($D$2:D38,D38,$E$2:E38,E38)</f>
-        <v>UI-Clutter-3</v>
+        <f>D38&amp;"-"&amp;E38&amp;"-"&amp;COUNTIFS($D$4:D38,D38,$E$4:E38,E38)</f>
+        <v>Subscription-Paywall-6</v>
       </c>
       <c r="K38" s="1">
-        <f t="shared" si="3"/>
-        <v>4</v>
+        <f t="shared" ref="K38:K69" si="3">COUNTIFS($D$4:$D$227,D38,$E$4:$E$227,E38)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>258</v>
@@ -11507,29 +11468,29 @@
         <v>Future</v>
       </c>
       <c r="J39" s="4" t="str">
-        <f>D39&amp;"-"&amp;E39&amp;"-"&amp;COUNTIFS($D$2:D39,D39,$E$2:E39,E39)</f>
-        <v>Bug-Notifications-1</v>
+        <f>D39&amp;"-"&amp;E39&amp;"-"&amp;COUNTIFS($D$4:D39,D39,$E$4:E39,E39)</f>
+        <v>Bug-Uncategorized-1</v>
       </c>
       <c r="K39" s="1">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>257</v>
@@ -11540,36 +11501,36 @@
       </c>
       <c r="H40" s="1" t="str">
         <f>IFERROR(VLOOKUP(D40&amp;"-"&amp;E40,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Reliable Sync</v>
+        <v>Setup Efficiency</v>
       </c>
       <c r="I40" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D40&amp;"-"&amp;E40,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-04</v>
+        <v>SR-03</v>
       </c>
       <c r="J40" s="4" t="str">
-        <f>D40&amp;"-"&amp;E40&amp;"-"&amp;COUNTIFS($D$2:D40,D40,$E$2:E40,E40)</f>
-        <v>Bug-Calendar-2</v>
+        <f>D40&amp;"-"&amp;E40&amp;"-"&amp;COUNTIFS($D$4:D40,D40,$E$4:E40,E40)</f>
+        <v>UI-Clutter-3</v>
       </c>
       <c r="K40" s="1">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>258</v>
@@ -11580,76 +11541,76 @@
       </c>
       <c r="H41" s="1" t="str">
         <f>IFERROR(VLOOKUP(D41&amp;"-"&amp;E41,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Reliable Sync</v>
+        <v>Support &amp; UX</v>
       </c>
       <c r="I41" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D41&amp;"-"&amp;E41,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-04</v>
+        <v>Future</v>
       </c>
       <c r="J41" s="4" t="str">
-        <f>D41&amp;"-"&amp;E41&amp;"-"&amp;COUNTIFS($D$2:D41,D41,$E$2:E41,E41)</f>
-        <v>Bug-Calendar-3</v>
+        <f>D41&amp;"-"&amp;E41&amp;"-"&amp;COUNTIFS($D$4:D41,D41,$E$4:E41,E41)</f>
+        <v>Bug-Notifications-1</v>
       </c>
       <c r="K41" s="1">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G42">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" s="1" t="str">
         <f>IFERROR(VLOOKUP(D42&amp;"-"&amp;E42,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Support &amp; UX</v>
+        <v>Reliable Sync</v>
       </c>
       <c r="I42" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D42&amp;"-"&amp;E42,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>Future</v>
+        <v>FR-04</v>
       </c>
       <c r="J42" s="4" t="str">
-        <f>D42&amp;"-"&amp;E42&amp;"-"&amp;COUNTIFS($D$2:D42,D42,$E$2:E42,E42)</f>
-        <v>Bug-Uncategorized-2</v>
+        <f>D42&amp;"-"&amp;E42&amp;"-"&amp;COUNTIFS($D$4:D42,D42,$E$4:E42,E42)</f>
+        <v>Bug-Calendar-2</v>
       </c>
       <c r="K42" s="1">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>173</v>
+        <v>20</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>258</v>
@@ -11660,43 +11621,43 @@
       </c>
       <c r="H43" s="1" t="str">
         <f>IFERROR(VLOOKUP(D43&amp;"-"&amp;E43,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Pricing &amp; Paywall</v>
+        <v>Reliable Sync</v>
       </c>
       <c r="I43" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D43&amp;"-"&amp;E43,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>Future</v>
+        <v>FR-04</v>
       </c>
       <c r="J43" s="4" t="str">
-        <f>D43&amp;"-"&amp;E43&amp;"-"&amp;COUNTIFS($D$2:D43,D43,$E$2:E43,E43)</f>
-        <v>Subscription-Refund-3</v>
+        <f>D43&amp;"-"&amp;E43&amp;"-"&amp;COUNTIFS($D$4:D43,D43,$E$4:E43,E43)</f>
+        <v>Bug-Calendar-3</v>
       </c>
       <c r="K43" s="1">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>174</v>
+        <v>20</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>241</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G44">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="1" t="str">
         <f>IFERROR(VLOOKUP(D44&amp;"-"&amp;E44,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
@@ -11707,8 +11668,8 @@
         <v>Future</v>
       </c>
       <c r="J44" s="4" t="str">
-        <f>D44&amp;"-"&amp;E44&amp;"-"&amp;COUNTIFS($D$2:D44,D44,$E$2:E44,E44)</f>
-        <v>Subscription-Uncategorized-1</v>
+        <f>D44&amp;"-"&amp;E44&amp;"-"&amp;COUNTIFS($D$4:D44,D44,$E$4:E44,E44)</f>
+        <v>Bug-Uncategorized-2</v>
       </c>
       <c r="K44" s="1">
         <f t="shared" si="3"/>
@@ -11717,59 +11678,59 @@
     </row>
     <row r="45" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G45">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" s="1" t="str">
         <f>IFERROR(VLOOKUP(D45&amp;"-"&amp;E45,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Platform Integrations</v>
+        <v>Pricing &amp; Paywall</v>
       </c>
       <c r="I45" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D45&amp;"-"&amp;E45,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
         <v>Future</v>
       </c>
       <c r="J45" s="4" t="str">
-        <f>D45&amp;"-"&amp;E45&amp;"-"&amp;COUNTIFS($D$2:D45,D45,$E$2:E45,E45)</f>
-        <v>Integrations-Apple_Watch-1</v>
+        <f>D45&amp;"-"&amp;E45&amp;"-"&amp;COUNTIFS($D$4:D45,D45,$E$4:E45,E45)</f>
+        <v>Subscription-Refund-3</v>
       </c>
       <c r="K45" s="1">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>257</v>
@@ -11780,76 +11741,76 @@
       </c>
       <c r="H46" s="1" t="str">
         <f>IFERROR(VLOOKUP(D46&amp;"-"&amp;E46,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Reliable Sync</v>
+        <v>Support &amp; UX</v>
       </c>
       <c r="I46" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D46&amp;"-"&amp;E46,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-04</v>
+        <v>Future</v>
       </c>
       <c r="J46" s="4" t="str">
-        <f>D46&amp;"-"&amp;E46&amp;"-"&amp;COUNTIFS($D$2:D46,D46,$E$2:E46,E46)</f>
-        <v>Bug-Calendar-4</v>
+        <f>D46&amp;"-"&amp;E46&amp;"-"&amp;COUNTIFS($D$4:D46,D46,$E$4:E46,E46)</f>
+        <v>Subscription-Uncategorized-1</v>
       </c>
       <c r="K46" s="1">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G47">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" s="1" t="str">
         <f>IFERROR(VLOOKUP(D47&amp;"-"&amp;E47,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Support &amp; UX</v>
+        <v>Platform Integrations</v>
       </c>
       <c r="I47" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D47&amp;"-"&amp;E47,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
         <v>Future</v>
       </c>
       <c r="J47" s="4" t="str">
-        <f>D47&amp;"-"&amp;E47&amp;"-"&amp;COUNTIFS($D$2:D47,D47,$E$2:E47,E47)</f>
-        <v>Integrations-Google_Calendar-1</v>
+        <f>D47&amp;"-"&amp;E47&amp;"-"&amp;COUNTIFS($D$4:D47,D47,$E$4:E47,E47)</f>
+        <v>Integrations-Apple_Watch-1</v>
       </c>
       <c r="K47" s="1">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>257</v>
@@ -11860,83 +11821,83 @@
       </c>
       <c r="H48" s="1" t="str">
         <f>IFERROR(VLOOKUP(D48&amp;"-"&amp;E48,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Support &amp; UX</v>
+        <v>Reliable Sync</v>
       </c>
       <c r="I48" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D48&amp;"-"&amp;E48,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>Future</v>
+        <v>FR-04</v>
       </c>
       <c r="J48" s="4" t="str">
-        <f>D48&amp;"-"&amp;E48&amp;"-"&amp;COUNTIFS($D$2:D48,D48,$E$2:E48,E48)</f>
-        <v>Other-Uncategorized-4</v>
+        <f>D48&amp;"-"&amp;E48&amp;"-"&amp;COUNTIFS($D$4:D48,D48,$E$4:E48,E48)</f>
+        <v>Bug-Calendar-4</v>
       </c>
       <c r="K48" s="1">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G49">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" s="1" t="str">
         <f>IFERROR(VLOOKUP(D49&amp;"-"&amp;E49,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Platform Integrations</v>
+        <v>Support &amp; UX</v>
       </c>
       <c r="I49" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D49&amp;"-"&amp;E49,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
         <v>Future</v>
       </c>
       <c r="J49" s="4" t="str">
-        <f>D49&amp;"-"&amp;E49&amp;"-"&amp;COUNTIFS($D$2:D49,D49,$E$2:E49,E49)</f>
-        <v>Integrations-Apple_Watch-2</v>
+        <f>D49&amp;"-"&amp;E49&amp;"-"&amp;COUNTIFS($D$4:D49,D49,$E$4:E49,E49)</f>
+        <v>Integrations-Google_Calendar-1</v>
       </c>
       <c r="K49" s="1">
         <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="113" customHeight="1" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>241</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G50">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" s="1" t="str">
         <f>IFERROR(VLOOKUP(D50&amp;"-"&amp;E50,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
@@ -11947,29 +11908,29 @@
         <v>Future</v>
       </c>
       <c r="J50" s="4" t="str">
-        <f>D50&amp;"-"&amp;E50&amp;"-"&amp;COUNTIFS($D$2:D50,D50,$E$2:E50,E50)</f>
-        <v>Bug-Uncategorized-3</v>
+        <f>D50&amp;"-"&amp;E50&amp;"-"&amp;COUNTIFS($D$4:D50,D50,$E$4:E50,E50)</f>
+        <v>Other-Uncategorized-4</v>
       </c>
       <c r="K50" s="1">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>257</v>
@@ -11980,43 +11941,43 @@
       </c>
       <c r="H51" s="1" t="str">
         <f>IFERROR(VLOOKUP(D51&amp;"-"&amp;E51,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Support &amp; UX</v>
+        <v>Platform Integrations</v>
       </c>
       <c r="I51" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D51&amp;"-"&amp;E51,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
         <v>Future</v>
       </c>
       <c r="J51" s="4" t="str">
-        <f>D51&amp;"-"&amp;E51&amp;"-"&amp;COUNTIFS($D$2:D51,D51,$E$2:E51,E51)</f>
-        <v>Integrations-Android-1</v>
+        <f>D51&amp;"-"&amp;E51&amp;"-"&amp;COUNTIFS($D$4:D51,D51,$E$4:E51,E51)</f>
+        <v>Integrations-Apple_Watch-2</v>
       </c>
       <c r="K51" s="1">
         <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="113" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>241</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G52">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" s="1" t="str">
         <f>IFERROR(VLOOKUP(D52&amp;"-"&amp;E52,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
@@ -12027,29 +11988,29 @@
         <v>Future</v>
       </c>
       <c r="J52" s="4" t="str">
-        <f>D52&amp;"-"&amp;E52&amp;"-"&amp;COUNTIFS($D$2:D52,D52,$E$2:E52,E52)</f>
-        <v>Other-Uncategorized-5</v>
+        <f>D52&amp;"-"&amp;E52&amp;"-"&amp;COUNTIFS($D$4:D52,D52,$E$4:E52,E52)</f>
+        <v>Bug-Uncategorized-3</v>
       </c>
       <c r="K52" s="1">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>257</v>
@@ -12060,36 +12021,36 @@
       </c>
       <c r="H53" s="1" t="str">
         <f>IFERROR(VLOOKUP(D53&amp;"-"&amp;E53,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Routine Engine</v>
+        <v>Support &amp; UX</v>
       </c>
       <c r="I53" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D53&amp;"-"&amp;E53,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>Future</v>
       </c>
       <c r="J53" s="4" t="str">
-        <f>D53&amp;"-"&amp;E53&amp;"-"&amp;COUNTIFS($D$2:D53,D53,$E$2:E53,E53)</f>
-        <v>Feature_Request-Routines-9</v>
+        <f>D53&amp;"-"&amp;E53&amp;"-"&amp;COUNTIFS($D$4:D53,D53,$E$4:E53,E53)</f>
+        <v>Integrations-Android-1</v>
       </c>
       <c r="K53" s="1">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>257</v>
@@ -12100,30 +12061,30 @@
       </c>
       <c r="H54" s="1" t="str">
         <f>IFERROR(VLOOKUP(D54&amp;"-"&amp;E54,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Routine Engine</v>
+        <v>Support &amp; UX</v>
       </c>
       <c r="I54" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D54&amp;"-"&amp;E54,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>Future</v>
       </c>
       <c r="J54" s="4" t="str">
-        <f>D54&amp;"-"&amp;E54&amp;"-"&amp;COUNTIFS($D$2:D54,D54,$E$2:E54,E54)</f>
-        <v>Feature_Request-Routines-10</v>
+        <f>D54&amp;"-"&amp;E54&amp;"-"&amp;COUNTIFS($D$4:D54,D54,$E$4:E54,E54)</f>
+        <v>Other-Uncategorized-5</v>
       </c>
       <c r="K54" s="1">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>7</v>
@@ -12132,11 +12093,11 @@
         <v>245</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G55">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" s="1" t="str">
         <f>IFERROR(VLOOKUP(D55&amp;"-"&amp;E55,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
@@ -12147,8 +12108,8 @@
         <v>FR-01</v>
       </c>
       <c r="J55" s="4" t="str">
-        <f>D55&amp;"-"&amp;E55&amp;"-"&amp;COUNTIFS($D$2:D55,D55,$E$2:E55,E55)</f>
-        <v>Feature_Request-Routines-11</v>
+        <f>D55&amp;"-"&amp;E55&amp;"-"&amp;COUNTIFS($D$4:D55,D55,$E$4:E55,E55)</f>
+        <v>Feature_Request-Routines-9</v>
       </c>
       <c r="K55" s="1">
         <f t="shared" si="3"/>
@@ -12157,19 +12118,19 @@
     </row>
     <row r="56" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>257</v>
@@ -12180,76 +12141,76 @@
       </c>
       <c r="H56" s="1" t="str">
         <f>IFERROR(VLOOKUP(D56&amp;"-"&amp;E56,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Support &amp; UX</v>
+        <v>Routine Engine</v>
       </c>
       <c r="I56" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D56&amp;"-"&amp;E56,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>Future</v>
+        <v>FR-01</v>
       </c>
       <c r="J56" s="4" t="str">
-        <f>D56&amp;"-"&amp;E56&amp;"-"&amp;COUNTIFS($D$2:D56,D56,$E$2:E56,E56)</f>
-        <v>Feature_Request-Alerts-1</v>
+        <f>D56&amp;"-"&amp;E56&amp;"-"&amp;COUNTIFS($D$4:D56,D56,$E$4:E56,E56)</f>
+        <v>Feature_Request-Routines-10</v>
       </c>
       <c r="K56" s="1">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G57">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" s="1" t="str">
         <f>IFERROR(VLOOKUP(D57&amp;"-"&amp;E57,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Support &amp; UX</v>
+        <v>Routine Engine</v>
       </c>
       <c r="I57" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D57&amp;"-"&amp;E57,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>Future</v>
+        <v>FR-01</v>
       </c>
       <c r="J57" s="4" t="str">
-        <f>D57&amp;"-"&amp;E57&amp;"-"&amp;COUNTIFS($D$2:D57,D57,$E$2:E57,E57)</f>
-        <v>Integrations-Google_Calendar-2</v>
+        <f>D57&amp;"-"&amp;E57&amp;"-"&amp;COUNTIFS($D$4:D57,D57,$E$4:E57,E57)</f>
+        <v>Feature_Request-Routines-11</v>
       </c>
       <c r="K57" s="1">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>257</v>
@@ -12260,36 +12221,36 @@
       </c>
       <c r="H58" s="1" t="str">
         <f>IFERROR(VLOOKUP(D58&amp;"-"&amp;E58,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Pricing &amp; Paywall</v>
+        <v>Support &amp; UX</v>
       </c>
       <c r="I58" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D58&amp;"-"&amp;E58,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
         <v>Future</v>
       </c>
       <c r="J58" s="4" t="str">
-        <f>D58&amp;"-"&amp;E58&amp;"-"&amp;COUNTIFS($D$2:D58,D58,$E$2:E58,E58)</f>
-        <v>Subscription-Paywall-7</v>
+        <f>D58&amp;"-"&amp;E58&amp;"-"&amp;COUNTIFS($D$4:D58,D58,$E$4:E58,E58)</f>
+        <v>Feature_Request-Alerts-1</v>
       </c>
       <c r="K58" s="1">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>257</v>
@@ -12300,36 +12261,36 @@
       </c>
       <c r="H59" s="1" t="str">
         <f>IFERROR(VLOOKUP(D59&amp;"-"&amp;E59,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Routine Engine</v>
+        <v>Support &amp; UX</v>
       </c>
       <c r="I59" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D59&amp;"-"&amp;E59,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>Future</v>
       </c>
       <c r="J59" s="4" t="str">
-        <f>D59&amp;"-"&amp;E59&amp;"-"&amp;COUNTIFS($D$2:D59,D59,$E$2:E59,E59)</f>
-        <v>Feature_Request-Routines-12</v>
+        <f>D59&amp;"-"&amp;E59&amp;"-"&amp;COUNTIFS($D$4:D59,D59,$E$4:E59,E59)</f>
+        <v>Integrations-Google_Calendar-2</v>
       </c>
       <c r="K59" s="1">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>257</v>
@@ -12340,30 +12301,30 @@
       </c>
       <c r="H60" s="1" t="str">
         <f>IFERROR(VLOOKUP(D60&amp;"-"&amp;E60,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Routine Engine</v>
+        <v>Pricing &amp; Paywall</v>
       </c>
       <c r="I60" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D60&amp;"-"&amp;E60,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>Future</v>
       </c>
       <c r="J60" s="4" t="str">
-        <f>D60&amp;"-"&amp;E60&amp;"-"&amp;COUNTIFS($D$2:D60,D60,$E$2:E60,E60)</f>
-        <v>Feature_Request-Routines-13</v>
+        <f>D60&amp;"-"&amp;E60&amp;"-"&amp;COUNTIFS($D$4:D60,D60,$E$4:E60,E60)</f>
+        <v>Subscription-Paywall-7</v>
       </c>
       <c r="K60" s="1">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>191</v>
+      <c r="C61" s="5" t="s">
+        <v>189</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>7</v>
@@ -12387,63 +12348,63 @@
         <v>FR-01</v>
       </c>
       <c r="J61" s="4" t="str">
-        <f>D61&amp;"-"&amp;E61&amp;"-"&amp;COUNTIFS($D$2:D61,D61,$E$2:E61,E61)</f>
-        <v>Feature_Request-Routines-14</v>
+        <f>D61&amp;"-"&amp;E61&amp;"-"&amp;COUNTIFS($D$4:D61,D61,$E$4:E61,E61)</f>
+        <v>Feature_Request-Routines-12</v>
       </c>
       <c r="K61" s="1">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="107" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>192</v>
+      <c r="C62" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>8</v>
+        <v>245</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G62">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" s="1" t="str">
         <f>IFERROR(VLOOKUP(D62&amp;"-"&amp;E62,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Reliable Sync</v>
+        <v>Routine Engine</v>
       </c>
       <c r="I62" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D62&amp;"-"&amp;E62,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-04</v>
+        <v>FR-01</v>
       </c>
       <c r="J62" s="4" t="str">
-        <f>D62&amp;"-"&amp;E62&amp;"-"&amp;COUNTIFS($D$2:D62,D62,$E$2:E62,E62)</f>
-        <v>Bug-UI-4</v>
+        <f>D62&amp;"-"&amp;E62&amp;"-"&amp;COUNTIFS($D$4:D62,D62,$E$4:E62,E62)</f>
+        <v>Feature_Request-Routines-13</v>
       </c>
       <c r="K62" s="1">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>7</v>
@@ -12467,143 +12428,143 @@
         <v>FR-01</v>
       </c>
       <c r="J63" s="4" t="str">
-        <f>D63&amp;"-"&amp;E63&amp;"-"&amp;COUNTIFS($D$2:D63,D63,$E$2:E63,E63)</f>
-        <v>Feature_Request-Routines-15</v>
+        <f>D63&amp;"-"&amp;E63&amp;"-"&amp;COUNTIFS($D$4:D63,D63,$E$4:E63,E63)</f>
+        <v>Feature_Request-Routines-14</v>
       </c>
       <c r="K63" s="1">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" ht="107" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E64" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E64" s="4" t="s">
-        <v>240</v>
-      </c>
       <c r="F64" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G64">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" s="1" t="str">
         <f>IFERROR(VLOOKUP(D64&amp;"-"&amp;E64,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Setup Efficiency</v>
+        <v>Reliable Sync</v>
       </c>
       <c r="I64" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D64&amp;"-"&amp;E64,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>SR-03</v>
+        <v>FR-04</v>
       </c>
       <c r="J64" s="4" t="str">
-        <f>D64&amp;"-"&amp;E64&amp;"-"&amp;COUNTIFS($D$2:D64,D64,$E$2:E64,E64)</f>
-        <v>UI-Clutter-4</v>
+        <f>D64&amp;"-"&amp;E64&amp;"-"&amp;COUNTIFS($D$4:D64,D64,$E$4:E64,E64)</f>
+        <v>Bug-UI-4</v>
       </c>
       <c r="K64" s="1">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>8</v>
+        <v>245</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G65">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" s="1" t="str">
         <f>IFERROR(VLOOKUP(D65&amp;"-"&amp;E65,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Reliable Sync</v>
+        <v>Routine Engine</v>
       </c>
       <c r="I65" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D65&amp;"-"&amp;E65,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-04</v>
+        <v>FR-01</v>
       </c>
       <c r="J65" s="4" t="str">
-        <f>D65&amp;"-"&amp;E65&amp;"-"&amp;COUNTIFS($D$2:D65,D65,$E$2:E65,E65)</f>
-        <v>Bug-UI-5</v>
+        <f>D65&amp;"-"&amp;E65&amp;"-"&amp;COUNTIFS($D$4:D65,D65,$E$4:E65,E65)</f>
+        <v>Feature_Request-Routines-15</v>
       </c>
       <c r="K65" s="1">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G66">
-        <f t="shared" ref="G66:G97" si="4">IF(F66="yes",1,0)</f>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="H66" s="1" t="str">
         <f>IFERROR(VLOOKUP(D66&amp;"-"&amp;E66,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Support &amp; UX</v>
+        <v>Setup Efficiency</v>
       </c>
       <c r="I66" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D66&amp;"-"&amp;E66,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>Future</v>
+        <v>SR-03</v>
       </c>
       <c r="J66" s="4" t="str">
-        <f>D66&amp;"-"&amp;E66&amp;"-"&amp;COUNTIFS($D$2:D66,D66,$E$2:E66,E66)</f>
-        <v>Integrations-Web_Desktop-1</v>
+        <f>D66&amp;"-"&amp;E66&amp;"-"&amp;COUNTIFS($D$4:D66,D66,$E$4:E66,E66)</f>
+        <v>UI-Clutter-4</v>
       </c>
       <c r="K66" s="1">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>6</v>
@@ -12615,7 +12576,7 @@
         <v>258</v>
       </c>
       <c r="G67">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H67" s="1" t="str">
@@ -12627,8 +12588,8 @@
         <v>FR-04</v>
       </c>
       <c r="J67" s="4" t="str">
-        <f>D67&amp;"-"&amp;E67&amp;"-"&amp;COUNTIFS($D$2:D67,D67,$E$2:E67,E67)</f>
-        <v>Bug-UI-6</v>
+        <f>D67&amp;"-"&amp;E67&amp;"-"&amp;COUNTIFS($D$4:D67,D67,$E$4:E67,E67)</f>
+        <v>Bug-UI-5</v>
       </c>
       <c r="K67" s="1">
         <f t="shared" si="3"/>
@@ -12637,146 +12598,146 @@
     </row>
     <row r="68" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C68" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G68">
+        <f t="shared" ref="G68:G99" si="4">IF(F68="yes",1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H68" s="1" t="str">
+        <f>IFERROR(VLOOKUP(D68&amp;"-"&amp;E68,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
+        <v>Support &amp; UX</v>
+      </c>
+      <c r="I68" s="1" t="str">
+        <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D68&amp;"-"&amp;E68,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
+        <v>Future</v>
+      </c>
+      <c r="J68" s="4" t="str">
+        <f>D68&amp;"-"&amp;E68&amp;"-"&amp;COUNTIFS($D$4:D68,D68,$E$4:E68,E68)</f>
+        <v>Integrations-Web_Desktop-1</v>
+      </c>
+      <c r="K68" s="1">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G69">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H69" s="1" t="str">
+        <f>IFERROR(VLOOKUP(D69&amp;"-"&amp;E69,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
+        <v>Reliable Sync</v>
+      </c>
+      <c r="I69" s="1" t="str">
+        <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D69&amp;"-"&amp;E69,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
+        <v>FR-04</v>
+      </c>
+      <c r="J69" s="4" t="str">
+        <f>D69&amp;"-"&amp;E69&amp;"-"&amp;COUNTIFS($D$4:D69,D69,$E$4:E69,E69)</f>
+        <v>Bug-UI-6</v>
+      </c>
+      <c r="K69" s="1">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D70" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E68" s="4" t="s">
+      <c r="E70" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="F70" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="G68">
+      <c r="G70">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H68" s="1" t="str">
-        <f>IFERROR(VLOOKUP(D68&amp;"-"&amp;E68,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
+      <c r="H70" s="1" t="str">
+        <f>IFERROR(VLOOKUP(D70&amp;"-"&amp;E70,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
         <v>Reliable Sync</v>
       </c>
-      <c r="I68" s="1" t="str">
-        <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D68&amp;"-"&amp;E68,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
+      <c r="I70" s="1" t="str">
+        <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D70&amp;"-"&amp;E70,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
         <v>FR-04</v>
       </c>
-      <c r="J68" s="4" t="str">
-        <f>D68&amp;"-"&amp;E68&amp;"-"&amp;COUNTIFS($D$2:D68,D68,$E$2:E68,E68)</f>
+      <c r="J70" s="4" t="str">
+        <f>D70&amp;"-"&amp;E70&amp;"-"&amp;COUNTIFS($D$4:D70,D70,$E$4:E70,E70)</f>
         <v>Bug-Calendar-5</v>
       </c>
-      <c r="K68" s="1">
-        <f t="shared" ref="K68:K99" si="5">COUNTIFS($D$2:$D$225,D68,$E$2:$E$225,E68)</f>
+      <c r="K70" s="1">
+        <f t="shared" ref="K70:K101" si="5">COUNTIFS($D$4:$D$227,D70,$E$4:$E$227,E70)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="1" t="s">
+    <row r="71" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B71" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C71" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D71" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E69" s="4" t="s">
+      <c r="E71" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="F69" s="1" t="s">
+      <c r="F71" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="G69">
+      <c r="G71">
         <f t="shared" si="4"/>
         <v>0</v>
-      </c>
-      <c r="H69" s="1" t="str">
-        <f>IFERROR(VLOOKUP(D69&amp;"-"&amp;E69,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Crash Prevention</v>
-      </c>
-      <c r="I69" s="1" t="str">
-        <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D69&amp;"-"&amp;E69,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>NFR-03</v>
-      </c>
-      <c r="J69" s="4" t="str">
-        <f>D69&amp;"-"&amp;E69&amp;"-"&amp;COUNTIFS($D$2:D69,D69,$E$2:E69,E69)</f>
-        <v>Performance-Crash-3</v>
-      </c>
-      <c r="K69" s="1">
-        <f t="shared" si="5"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="G70">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="H70" s="1" t="str">
-        <f>IFERROR(VLOOKUP(D70&amp;"-"&amp;E70,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Support &amp; UX</v>
-      </c>
-      <c r="I70" s="1" t="str">
-        <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D70&amp;"-"&amp;E70,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>Future</v>
-      </c>
-      <c r="J70" s="4" t="str">
-        <f>D70&amp;"-"&amp;E70&amp;"-"&amp;COUNTIFS($D$2:D70,D70,$E$2:E70,E70)</f>
-        <v>Integrations-Calendar-1</v>
-      </c>
-      <c r="K70" s="1">
-        <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E71" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="G71">
-        <f t="shared" si="4"/>
-        <v>1</v>
       </c>
       <c r="H71" s="1" t="str">
         <f>IFERROR(VLOOKUP(D71&amp;"-"&amp;E71,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
@@ -12787,8 +12748,8 @@
         <v>NFR-03</v>
       </c>
       <c r="J71" s="4" t="str">
-        <f>D71&amp;"-"&amp;E71&amp;"-"&amp;COUNTIFS($D$2:D71,D71,$E$2:E71,E71)</f>
-        <v>Performance-Crash-4</v>
+        <f>D71&amp;"-"&amp;E71&amp;"-"&amp;COUNTIFS($D$4:D71,D71,$E$4:E71,E71)</f>
+        <v>Performance-Crash-3</v>
       </c>
       <c r="K71" s="1">
         <f t="shared" si="5"/>
@@ -12797,19 +12758,19 @@
     </row>
     <row r="72" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>258</v>
@@ -12827,8 +12788,8 @@
         <v>Future</v>
       </c>
       <c r="J72" s="4" t="str">
-        <f>D72&amp;"-"&amp;E72&amp;"-"&amp;COUNTIFS($D$2:D72,D72,$E$2:E72,E72)</f>
-        <v>Subscription-High_Price-1</v>
+        <f>D72&amp;"-"&amp;E72&amp;"-"&amp;COUNTIFS($D$4:D72,D72,$E$4:E72,E72)</f>
+        <v>Integrations-Calendar-1</v>
       </c>
       <c r="K72" s="1">
         <f t="shared" si="5"/>
@@ -12837,66 +12798,66 @@
     </row>
     <row r="73" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" s="1" t="str">
         <f>IFERROR(VLOOKUP(D73&amp;"-"&amp;E73,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Reliable Sync</v>
+        <v>Crash Prevention</v>
       </c>
       <c r="I73" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D73&amp;"-"&amp;E73,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-04</v>
+        <v>NFR-03</v>
       </c>
       <c r="J73" s="4" t="str">
-        <f>D73&amp;"-"&amp;E73&amp;"-"&amp;COUNTIFS($D$2:D73,D73,$E$2:E73,E73)</f>
-        <v>Bug-Calendar-6</v>
+        <f>D73&amp;"-"&amp;E73&amp;"-"&amp;COUNTIFS($D$4:D73,D73,$E$4:E73,E73)</f>
+        <v>Performance-Crash-4</v>
       </c>
       <c r="K73" s="1">
         <f t="shared" si="5"/>
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C74" s="5" t="s">
-        <v>176</v>
+      <c r="C74" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G74">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74" s="1" t="str">
         <f>IFERROR(VLOOKUP(D74&amp;"-"&amp;E74,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
@@ -12907,23 +12868,23 @@
         <v>Future</v>
       </c>
       <c r="J74" s="4" t="str">
-        <f>D74&amp;"-"&amp;E74&amp;"-"&amp;COUNTIFS($D$2:D74,D74,$E$2:E74,E74)</f>
-        <v>Bug-Routines-1</v>
+        <f>D74&amp;"-"&amp;E74&amp;"-"&amp;COUNTIFS($D$4:D74,D74,$E$4:E74,E74)</f>
+        <v>Subscription-High_Price-1</v>
       </c>
       <c r="K74" s="1">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" ht="107" customHeight="1" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C75" s="5" t="s">
-        <v>180</v>
+      <c r="C75" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>6</v>
@@ -12932,11 +12893,11 @@
         <v>238</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G75">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" s="1" t="str">
         <f>IFERROR(VLOOKUP(D75&amp;"-"&amp;E75,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
@@ -12947,8 +12908,8 @@
         <v>FR-04</v>
       </c>
       <c r="J75" s="4" t="str">
-        <f>D75&amp;"-"&amp;E75&amp;"-"&amp;COUNTIFS($D$2:D75,D75,$E$2:E75,E75)</f>
-        <v>Bug-Calendar-7</v>
+        <f>D75&amp;"-"&amp;E75&amp;"-"&amp;COUNTIFS($D$4:D75,D75,$E$4:E75,E75)</f>
+        <v>Bug-Calendar-6</v>
       </c>
       <c r="K75" s="1">
         <f t="shared" si="5"/>
@@ -12957,19 +12918,19 @@
     </row>
     <row r="76" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>197</v>
+      <c r="C76" s="5" t="s">
+        <v>176</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>8</v>
+        <v>245</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>257</v>
@@ -12980,36 +12941,36 @@
       </c>
       <c r="H76" s="1" t="str">
         <f>IFERROR(VLOOKUP(D76&amp;"-"&amp;E76,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Reliable Sync</v>
+        <v>Support &amp; UX</v>
       </c>
       <c r="I76" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D76&amp;"-"&amp;E76,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-04</v>
+        <v>Future</v>
       </c>
       <c r="J76" s="4" t="str">
-        <f>D76&amp;"-"&amp;E76&amp;"-"&amp;COUNTIFS($D$2:D76,D76,$E$2:E76,E76)</f>
-        <v>Bug-UI-7</v>
+        <f>D76&amp;"-"&amp;E76&amp;"-"&amp;COUNTIFS($D$4:D76,D76,$E$4:E76,E76)</f>
+        <v>Bug-Routines-1</v>
       </c>
       <c r="K76" s="1">
         <f t="shared" si="5"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="107" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C77" s="1" t="s">
-        <v>199</v>
+      <c r="C77" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>258</v>
@@ -13020,36 +12981,36 @@
       </c>
       <c r="H77" s="1" t="str">
         <f>IFERROR(VLOOKUP(D77&amp;"-"&amp;E77,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Crash Prevention</v>
+        <v>Reliable Sync</v>
       </c>
       <c r="I77" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D77&amp;"-"&amp;E77,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>NFR-03</v>
+        <v>FR-04</v>
       </c>
       <c r="J77" s="4" t="str">
-        <f>D77&amp;"-"&amp;E77&amp;"-"&amp;COUNTIFS($D$2:D77,D77,$E$2:E77,E77)</f>
-        <v>Performance-Crash-5</v>
+        <f>D77&amp;"-"&amp;E77&amp;"-"&amp;COUNTIFS($D$4:D77,D77,$E$4:E77,E77)</f>
+        <v>Bug-Calendar-7</v>
       </c>
       <c r="K77" s="1">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C78" s="5" t="s">
-        <v>175</v>
+      <c r="C78" s="1" t="s">
+        <v>197</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>238</v>
+        <v>8</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>257</v>
@@ -13067,69 +13028,69 @@
         <v>FR-04</v>
       </c>
       <c r="J78" s="4" t="str">
-        <f>D78&amp;"-"&amp;E78&amp;"-"&amp;COUNTIFS($D$2:D78,D78,$E$2:E78,E78)</f>
-        <v>Bug-Calendar-8</v>
+        <f>D78&amp;"-"&amp;E78&amp;"-"&amp;COUNTIFS($D$4:D78,D78,$E$4:E78,E78)</f>
+        <v>Bug-UI-7</v>
       </c>
       <c r="K78" s="1">
         <f t="shared" si="5"/>
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G79">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" s="1" t="str">
         <f>IFERROR(VLOOKUP(D79&amp;"-"&amp;E79,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Support &amp; UX</v>
+        <v>Crash Prevention</v>
       </c>
       <c r="I79" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D79&amp;"-"&amp;E79,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>Future</v>
+        <v>NFR-03</v>
       </c>
       <c r="J79" s="4" t="str">
-        <f>D79&amp;"-"&amp;E79&amp;"-"&amp;COUNTIFS($D$2:D79,D79,$E$2:E79,E79)</f>
-        <v>Other-Uncategorized-6</v>
+        <f>D79&amp;"-"&amp;E79&amp;"-"&amp;COUNTIFS($D$4:D79,D79,$E$4:E79,E79)</f>
+        <v>Performance-Crash-5</v>
       </c>
       <c r="K79" s="1">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>204</v>
+        <v>21</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>175</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>257</v>
@@ -13140,36 +13101,36 @@
       </c>
       <c r="H80" s="1" t="str">
         <f>IFERROR(VLOOKUP(D80&amp;"-"&amp;E80,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Support &amp; UX</v>
+        <v>Reliable Sync</v>
       </c>
       <c r="I80" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D80&amp;"-"&amp;E80,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>Future</v>
+        <v>FR-04</v>
       </c>
       <c r="J80" s="4" t="str">
-        <f>D80&amp;"-"&amp;E80&amp;"-"&amp;COUNTIFS($D$2:D80,D80,$E$2:E80,E80)</f>
-        <v>Subscription-High_Price-2</v>
+        <f>D80&amp;"-"&amp;E80&amp;"-"&amp;COUNTIFS($D$4:D80,D80,$E$4:E80,E80)</f>
+        <v>Bug-Calendar-8</v>
       </c>
       <c r="K80" s="1">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>205</v>
+        <v>22</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>257</v>
@@ -13180,36 +13141,36 @@
       </c>
       <c r="H81" s="1" t="str">
         <f>IFERROR(VLOOKUP(D81&amp;"-"&amp;E81,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Routine Engine</v>
+        <v>Support &amp; UX</v>
       </c>
       <c r="I81" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D81&amp;"-"&amp;E81,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>Future</v>
       </c>
       <c r="J81" s="4" t="str">
-        <f>D81&amp;"-"&amp;E81&amp;"-"&amp;COUNTIFS($D$2:D81,D81,$E$2:E81,E81)</f>
-        <v>Feature_Request-Routines-16</v>
+        <f>D81&amp;"-"&amp;E81&amp;"-"&amp;COUNTIFS($D$4:D81,D81,$E$4:E81,E81)</f>
+        <v>Other-Uncategorized-6</v>
       </c>
       <c r="K81" s="1">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>206</v>
+        <v>22</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>204</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>257</v>
@@ -13227,29 +13188,29 @@
         <v>Future</v>
       </c>
       <c r="J82" s="4" t="str">
-        <f>D82&amp;"-"&amp;E82&amp;"-"&amp;COUNTIFS($D$2:D82,D82,$E$2:E82,E82)</f>
-        <v>Feature_Request-Uncategorized-1</v>
+        <f>D82&amp;"-"&amp;E82&amp;"-"&amp;COUNTIFS($D$4:D82,D82,$E$4:E82,E82)</f>
+        <v>Subscription-High_Price-2</v>
       </c>
       <c r="K82" s="1">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>257</v>
@@ -13260,36 +13221,36 @@
       </c>
       <c r="H83" s="1" t="str">
         <f>IFERROR(VLOOKUP(D83&amp;"-"&amp;E83,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Support &amp; UX</v>
+        <v>Routine Engine</v>
       </c>
       <c r="I83" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D83&amp;"-"&amp;E83,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>Future</v>
+        <v>FR-01</v>
       </c>
       <c r="J83" s="4" t="str">
-        <f>D83&amp;"-"&amp;E83&amp;"-"&amp;COUNTIFS($D$2:D83,D83,$E$2:E83,E83)</f>
-        <v>Other-Uncategorized-7</v>
+        <f>D83&amp;"-"&amp;E83&amp;"-"&amp;COUNTIFS($D$4:D83,D83,$E$4:E83,E83)</f>
+        <v>Feature_Request-Routines-16</v>
       </c>
       <c r="K83" s="1">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>257</v>
@@ -13300,36 +13261,36 @@
       </c>
       <c r="H84" s="1" t="str">
         <f>IFERROR(VLOOKUP(D84&amp;"-"&amp;E84,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Routine Engine</v>
+        <v>Support &amp; UX</v>
       </c>
       <c r="I84" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D84&amp;"-"&amp;E84,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>Future</v>
       </c>
       <c r="J84" s="4" t="str">
-        <f>D84&amp;"-"&amp;E84&amp;"-"&amp;COUNTIFS($D$2:D84,D84,$E$2:E84,E84)</f>
-        <v>Feature_Request-Routines-17</v>
+        <f>D84&amp;"-"&amp;E84&amp;"-"&amp;COUNTIFS($D$4:D84,D84,$E$4:E84,E84)</f>
+        <v>Feature_Request-Uncategorized-1</v>
       </c>
       <c r="K84" s="1">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>257</v>
@@ -13347,29 +13308,29 @@
         <v>Future</v>
       </c>
       <c r="J85" s="4" t="str">
-        <f>D85&amp;"-"&amp;E85&amp;"-"&amp;COUNTIFS($D$2:D85,D85,$E$2:E85,E85)</f>
-        <v>Feature_Request-Widgets-1</v>
+        <f>D85&amp;"-"&amp;E85&amp;"-"&amp;COUNTIFS($D$4:D85,D85,$E$4:E85,E85)</f>
+        <v>Other-Uncategorized-7</v>
       </c>
       <c r="K85" s="1">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C86" s="6" t="s">
-        <v>210</v>
+      <c r="C86" s="5" t="s">
+        <v>208</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>257</v>
@@ -13380,36 +13341,36 @@
       </c>
       <c r="H86" s="1" t="str">
         <f>IFERROR(VLOOKUP(D86&amp;"-"&amp;E86,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Support &amp; UX</v>
+        <v>Routine Engine</v>
       </c>
       <c r="I86" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D86&amp;"-"&amp;E86,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>Future</v>
+        <v>FR-01</v>
       </c>
       <c r="J86" s="4" t="str">
-        <f>D86&amp;"-"&amp;E86&amp;"-"&amp;COUNTIFS($D$2:D86,D86,$E$2:E86,E86)</f>
-        <v>Feature_Request-Uncategorized-2</v>
+        <f>D86&amp;"-"&amp;E86&amp;"-"&amp;COUNTIFS($D$4:D86,D86,$E$4:E86,E86)</f>
+        <v>Feature_Request-Routines-17</v>
       </c>
       <c r="K86" s="1">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>257</v>
@@ -13420,36 +13381,36 @@
       </c>
       <c r="H87" s="1" t="str">
         <f>IFERROR(VLOOKUP(D87&amp;"-"&amp;E87,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Routine Engine</v>
+        <v>Support &amp; UX</v>
       </c>
       <c r="I87" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D87&amp;"-"&amp;E87,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>Future</v>
       </c>
       <c r="J87" s="4" t="str">
-        <f>D87&amp;"-"&amp;E87&amp;"-"&amp;COUNTIFS($D$2:D87,D87,$E$2:E87,E87)</f>
-        <v>Feature_Request-Routines-18</v>
+        <f>D87&amp;"-"&amp;E87&amp;"-"&amp;COUNTIFS($D$4:D87,D87,$E$4:E87,E87)</f>
+        <v>Feature_Request-Widgets-1</v>
       </c>
       <c r="K87" s="1">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C88" s="5" t="s">
-        <v>212</v>
+      <c r="C88" s="6" t="s">
+        <v>210</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>257</v>
@@ -13467,29 +13428,29 @@
         <v>Future</v>
       </c>
       <c r="J88" s="4" t="str">
-        <f>D88&amp;"-"&amp;E88&amp;"-"&amp;COUNTIFS($D$2:D88,D88,$E$2:E88,E88)</f>
-        <v>Bug-AI-1</v>
+        <f>D88&amp;"-"&amp;E88&amp;"-"&amp;COUNTIFS($D$4:D88,D88,$E$4:E88,E88)</f>
+        <v>Feature_Request-Uncategorized-2</v>
       </c>
       <c r="K88" s="1">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C89" s="6" t="s">
-        <v>213</v>
+      <c r="C89" s="5" t="s">
+        <v>211</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>257</v>
@@ -13500,36 +13461,36 @@
       </c>
       <c r="H89" s="1" t="str">
         <f>IFERROR(VLOOKUP(D89&amp;"-"&amp;E89,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Pricing &amp; Paywall</v>
+        <v>Routine Engine</v>
       </c>
       <c r="I89" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D89&amp;"-"&amp;E89,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>Future</v>
+        <v>FR-01</v>
       </c>
       <c r="J89" s="4" t="str">
-        <f>D89&amp;"-"&amp;E89&amp;"-"&amp;COUNTIFS($D$2:D89,D89,$E$2:E89,E89)</f>
-        <v>Subscription-Paywall-8</v>
+        <f>D89&amp;"-"&amp;E89&amp;"-"&amp;COUNTIFS($D$4:D89,D89,$E$4:E89,E89)</f>
+        <v>Feature_Request-Routines-18</v>
       </c>
       <c r="K89" s="1">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>257</v>
@@ -13547,29 +13508,29 @@
         <v>Future</v>
       </c>
       <c r="J90" s="4" t="str">
-        <f>D90&amp;"-"&amp;E90&amp;"-"&amp;COUNTIFS($D$2:D90,D90,$E$2:E90,E90)</f>
-        <v>Subscription-Uncategorized-2</v>
+        <f>D90&amp;"-"&amp;E90&amp;"-"&amp;COUNTIFS($D$4:D90,D90,$E$4:E90,E90)</f>
+        <v>Bug-AI-1</v>
       </c>
       <c r="K90" s="1">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C91" s="5" t="s">
-        <v>215</v>
+      <c r="C91" s="6" t="s">
+        <v>213</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>257</v>
@@ -13580,36 +13541,36 @@
       </c>
       <c r="H91" s="1" t="str">
         <f>IFERROR(VLOOKUP(D91&amp;"-"&amp;E91,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Support &amp; UX</v>
+        <v>Pricing &amp; Paywall</v>
       </c>
       <c r="I91" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D91&amp;"-"&amp;E91,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
         <v>Future</v>
       </c>
       <c r="J91" s="4" t="str">
-        <f>D91&amp;"-"&amp;E91&amp;"-"&amp;COUNTIFS($D$2:D91,D91,$E$2:E91,E91)</f>
-        <v>Feature_Request-Uncategorized-3</v>
+        <f>D91&amp;"-"&amp;E91&amp;"-"&amp;COUNTIFS($D$4:D91,D91,$E$4:E91,E91)</f>
+        <v>Subscription-Paywall-8</v>
       </c>
       <c r="K91" s="1">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>257</v>
@@ -13627,29 +13588,29 @@
         <v>Future</v>
       </c>
       <c r="J92" s="4" t="str">
-        <f>D92&amp;"-"&amp;E92&amp;"-"&amp;COUNTIFS($D$2:D92,D92,$E$2:E92,E92)</f>
-        <v>Integrations-Calendar-2</v>
+        <f>D92&amp;"-"&amp;E92&amp;"-"&amp;COUNTIFS($D$4:D92,D92,$E$4:E92,E92)</f>
+        <v>Subscription-Uncategorized-2</v>
       </c>
       <c r="K92" s="1">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>217</v>
+      <c r="C93" s="5" t="s">
+        <v>215</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>257</v>
@@ -13667,8 +13628,8 @@
         <v>Future</v>
       </c>
       <c r="J93" s="4" t="str">
-        <f>D93&amp;"-"&amp;E93&amp;"-"&amp;COUNTIFS($D$2:D93,D93,$E$2:E93,E93)</f>
-        <v>Integrations-Android-2</v>
+        <f>D93&amp;"-"&amp;E93&amp;"-"&amp;COUNTIFS($D$4:D93,D93,$E$4:E93,E93)</f>
+        <v>Feature_Request-Uncategorized-3</v>
       </c>
       <c r="K93" s="1">
         <f t="shared" si="5"/>
@@ -13677,19 +13638,19 @@
     </row>
     <row r="94" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>257</v>
@@ -13707,23 +13668,23 @@
         <v>Future</v>
       </c>
       <c r="J94" s="4" t="str">
-        <f>D94&amp;"-"&amp;E94&amp;"-"&amp;COUNTIFS($D$2:D94,D94,$E$2:E94,E94)</f>
-        <v>Integrations-Android-3</v>
+        <f>D94&amp;"-"&amp;E94&amp;"-"&amp;COUNTIFS($D$4:D94,D94,$E$4:E94,E94)</f>
+        <v>Integrations-Calendar-2</v>
       </c>
       <c r="K94" s="1">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C95" s="5" t="s">
-        <v>219</v>
+      <c r="C95" s="1" t="s">
+        <v>217</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>10</v>
@@ -13747,8 +13708,8 @@
         <v>Future</v>
       </c>
       <c r="J95" s="4" t="str">
-        <f>D95&amp;"-"&amp;E95&amp;"-"&amp;COUNTIFS($D$2:D95,D95,$E$2:E95,E95)</f>
-        <v>Integrations-Android-4</v>
+        <f>D95&amp;"-"&amp;E95&amp;"-"&amp;COUNTIFS($D$4:D95,D95,$E$4:E95,E95)</f>
+        <v>Integrations-Android-2</v>
       </c>
       <c r="K95" s="1">
         <f t="shared" si="5"/>
@@ -13757,19 +13718,19 @@
     </row>
     <row r="96" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C96" s="1" t="s">
-        <v>220</v>
+      <c r="C96" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>257</v>
@@ -13780,36 +13741,36 @@
       </c>
       <c r="H96" s="1" t="str">
         <f>IFERROR(VLOOKUP(D96&amp;"-"&amp;E96,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Platform Integrations</v>
+        <v>Support &amp; UX</v>
       </c>
       <c r="I96" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D96&amp;"-"&amp;E96,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
         <v>Future</v>
       </c>
       <c r="J96" s="4" t="str">
-        <f>D96&amp;"-"&amp;E96&amp;"-"&amp;COUNTIFS($D$2:D96,D96,$E$2:E96,E96)</f>
-        <v>Integrations-Apple_Watch-3</v>
+        <f>D96&amp;"-"&amp;E96&amp;"-"&amp;COUNTIFS($D$4:D96,D96,$E$4:E96,E96)</f>
+        <v>Integrations-Android-3</v>
       </c>
       <c r="K96" s="1">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>257</v>
@@ -13827,8 +13788,8 @@
         <v>Future</v>
       </c>
       <c r="J97" s="4" t="str">
-        <f>D97&amp;"-"&amp;E97&amp;"-"&amp;COUNTIFS($D$2:D97,D97,$E$2:E97,E97)</f>
-        <v>Subscription-Uncategorized-3</v>
+        <f>D97&amp;"-"&amp;E97&amp;"-"&amp;COUNTIFS($D$4:D97,D97,$E$4:E97,E97)</f>
+        <v>Integrations-Android-4</v>
       </c>
       <c r="K97" s="1">
         <f t="shared" si="5"/>
@@ -13837,56 +13798,56 @@
     </row>
     <row r="98" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C98" s="5" t="s">
-        <v>222</v>
+      <c r="C98" s="1" t="s">
+        <v>220</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>257</v>
       </c>
       <c r="G98">
-        <f t="shared" ref="G98:G114" si="6">IF(F98="yes",1,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H98" s="1" t="str">
         <f>IFERROR(VLOOKUP(D98&amp;"-"&amp;E98,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Support &amp; UX</v>
+        <v>Platform Integrations</v>
       </c>
       <c r="I98" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D98&amp;"-"&amp;E98,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
         <v>Future</v>
       </c>
       <c r="J98" s="4" t="str">
-        <f>D98&amp;"-"&amp;E98&amp;"-"&amp;COUNTIFS($D$2:D98,D98,$E$2:E98,E98)</f>
-        <v>Subscription-Uncategorized-4</v>
+        <f>D98&amp;"-"&amp;E98&amp;"-"&amp;COUNTIFS($D$4:D98,D98,$E$4:E98,E98)</f>
+        <v>Integrations-Apple_Watch-3</v>
       </c>
       <c r="K98" s="1">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>241</v>
@@ -13895,7 +13856,7 @@
         <v>257</v>
       </c>
       <c r="G99">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H99" s="1" t="str">
@@ -13907,8 +13868,8 @@
         <v>Future</v>
       </c>
       <c r="J99" s="4" t="str">
-        <f>D99&amp;"-"&amp;E99&amp;"-"&amp;COUNTIFS($D$2:D99,D99,$E$2:E99,E99)</f>
-        <v>Feature_Request-Uncategorized-4</v>
+        <f>D99&amp;"-"&amp;E99&amp;"-"&amp;COUNTIFS($D$4:D99,D99,$E$4:E99,E99)</f>
+        <v>Subscription-Uncategorized-3</v>
       </c>
       <c r="K99" s="1">
         <f t="shared" si="5"/>
@@ -13917,56 +13878,56 @@
     </row>
     <row r="100" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>257</v>
       </c>
       <c r="G100">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="G100:G116" si="6">IF(F100="yes",1,0)</f>
         <v>0</v>
       </c>
       <c r="H100" s="1" t="str">
         <f>IFERROR(VLOOKUP(D100&amp;"-"&amp;E100,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Platform Integrations</v>
+        <v>Support &amp; UX</v>
       </c>
       <c r="I100" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D100&amp;"-"&amp;E100,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
         <v>Future</v>
       </c>
       <c r="J100" s="4" t="str">
-        <f>D100&amp;"-"&amp;E100&amp;"-"&amp;COUNTIFS($D$2:D100,D100,$E$2:E100,E100)</f>
-        <v>Integrations-Apple_Watch-4</v>
+        <f>D100&amp;"-"&amp;E100&amp;"-"&amp;COUNTIFS($D$4:D100,D100,$E$4:E100,E100)</f>
+        <v>Subscription-Uncategorized-4</v>
       </c>
       <c r="K100" s="1">
-        <f t="shared" ref="K100:K114" si="7">COUNTIFS($D$2:$D$225,D100,$E$2:$E$225,E100)</f>
-        <v>5</v>
+        <f t="shared" si="5"/>
+        <v>4</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E101" s="4" t="s">
         <v>241</v>
@@ -13987,29 +13948,29 @@
         <v>Future</v>
       </c>
       <c r="J101" s="4" t="str">
-        <f>D101&amp;"-"&amp;E101&amp;"-"&amp;COUNTIFS($D$2:D101,D101,$E$2:E101,E101)</f>
-        <v>Other-Uncategorized-8</v>
+        <f>D101&amp;"-"&amp;E101&amp;"-"&amp;COUNTIFS($D$4:D101,D101,$E$4:E101,E101)</f>
+        <v>Feature_Request-Uncategorized-4</v>
       </c>
       <c r="K101" s="1">
-        <f t="shared" si="7"/>
-        <v>8</v>
+        <f t="shared" si="5"/>
+        <v>4</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>257</v>
@@ -14020,43 +13981,43 @@
       </c>
       <c r="H102" s="1" t="str">
         <f>IFERROR(VLOOKUP(D102&amp;"-"&amp;E102,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Reliable Sync</v>
+        <v>Platform Integrations</v>
       </c>
       <c r="I102" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D102&amp;"-"&amp;E102,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-04</v>
+        <v>Future</v>
       </c>
       <c r="J102" s="4" t="str">
-        <f>D102&amp;"-"&amp;E102&amp;"-"&amp;COUNTIFS($D$2:D102,D102,$E$2:E102,E102)</f>
-        <v>Bug-Calendar-9</v>
+        <f>D102&amp;"-"&amp;E102&amp;"-"&amp;COUNTIFS($D$4:D102,D102,$E$4:E102,E102)</f>
+        <v>Integrations-Apple_Watch-4</v>
       </c>
       <c r="K102" s="1">
-        <f t="shared" si="7"/>
-        <v>9</v>
+        <f t="shared" ref="K102:K116" si="7">COUNTIFS($D$4:$D$227,D102,$E$4:$E$227,E102)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G103">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H103" s="1" t="str">
         <f>IFERROR(VLOOKUP(D103&amp;"-"&amp;E103,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
@@ -14067,29 +14028,29 @@
         <v>Future</v>
       </c>
       <c r="J103" s="4" t="str">
-        <f>D103&amp;"-"&amp;E103&amp;"-"&amp;COUNTIFS($D$2:D103,D103,$E$2:E103,E103)</f>
-        <v>Bug-Timers-1</v>
+        <f>D103&amp;"-"&amp;E103&amp;"-"&amp;COUNTIFS($D$4:D103,D103,$E$4:E103,E103)</f>
+        <v>Other-Uncategorized-8</v>
       </c>
       <c r="K103" s="1">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C104" s="1" t="s">
-        <v>228</v>
+      <c r="C104" s="5" t="s">
+        <v>226</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>257</v>
@@ -14100,43 +14061,43 @@
       </c>
       <c r="H104" s="1" t="str">
         <f>IFERROR(VLOOKUP(D104&amp;"-"&amp;E104,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Routine Engine</v>
+        <v>Reliable Sync</v>
       </c>
       <c r="I104" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D104&amp;"-"&amp;E104,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-04</v>
       </c>
       <c r="J104" s="4" t="str">
-        <f>D104&amp;"-"&amp;E104&amp;"-"&amp;COUNTIFS($D$2:D104,D104,$E$2:E104,E104)</f>
-        <v>Feature_Request-Routines-19</v>
+        <f>D104&amp;"-"&amp;E104&amp;"-"&amp;COUNTIFS($D$4:D104,D104,$E$4:E104,E104)</f>
+        <v>Bug-Calendar-9</v>
       </c>
       <c r="K104" s="1">
         <f t="shared" si="7"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>229</v>
+      <c r="C105" s="5" t="s">
+        <v>227</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G105">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" s="1" t="str">
         <f>IFERROR(VLOOKUP(D105&amp;"-"&amp;E105,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
@@ -14147,23 +14108,23 @@
         <v>Future</v>
       </c>
       <c r="J105" s="4" t="str">
-        <f>D105&amp;"-"&amp;E105&amp;"-"&amp;COUNTIFS($D$2:D105,D105,$E$2:E105,E105)</f>
-        <v>UI-Uncategorized-4</v>
+        <f>D105&amp;"-"&amp;E105&amp;"-"&amp;COUNTIFS($D$4:D105,D105,$E$4:E105,E105)</f>
+        <v>Bug-Timers-1</v>
       </c>
       <c r="K105" s="1">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>7</v>
@@ -14187,8 +14148,8 @@
         <v>FR-01</v>
       </c>
       <c r="J106" s="4" t="str">
-        <f>D106&amp;"-"&amp;E106&amp;"-"&amp;COUNTIFS($D$2:D106,D106,$E$2:E106,E106)</f>
-        <v>Feature_Request-Routines-20</v>
+        <f>D106&amp;"-"&amp;E106&amp;"-"&amp;COUNTIFS($D$4:D106,D106,$E$4:E106,E106)</f>
+        <v>Feature_Request-Routines-19</v>
       </c>
       <c r="K106" s="1">
         <f t="shared" si="7"/>
@@ -14197,19 +14158,19 @@
     </row>
     <row r="107" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>257</v>
@@ -14220,70 +14181,70 @@
       </c>
       <c r="H107" s="1" t="str">
         <f>IFERROR(VLOOKUP(D107&amp;"-"&amp;E107,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Routine Engine</v>
+        <v>Support &amp; UX</v>
       </c>
       <c r="I107" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D107&amp;"-"&amp;E107,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>Future</v>
       </c>
       <c r="J107" s="4" t="str">
-        <f>D107&amp;"-"&amp;E107&amp;"-"&amp;COUNTIFS($D$2:D107,D107,$E$2:E107,E107)</f>
-        <v>Feature_Request-Routines-21</v>
+        <f>D107&amp;"-"&amp;E107&amp;"-"&amp;COUNTIFS($D$4:D107,D107,$E$4:E107,E107)</f>
+        <v>UI-Uncategorized-4</v>
       </c>
       <c r="K107" s="1">
         <f t="shared" si="7"/>
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G108">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H108" s="1" t="str">
         <f>IFERROR(VLOOKUP(D108&amp;"-"&amp;E108,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Platform Integrations</v>
+        <v>Routine Engine</v>
       </c>
       <c r="I108" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D108&amp;"-"&amp;E108,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>Future</v>
+        <v>FR-01</v>
       </c>
       <c r="J108" s="4" t="str">
-        <f>D108&amp;"-"&amp;E108&amp;"-"&amp;COUNTIFS($D$2:D108,D108,$E$2:E108,E108)</f>
-        <v>Integrations-Apple_Watch-5</v>
+        <f>D108&amp;"-"&amp;E108&amp;"-"&amp;COUNTIFS($D$4:D108,D108,$E$4:E108,E108)</f>
+        <v>Feature_Request-Routines-20</v>
       </c>
       <c r="K108" s="1">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>7</v>
@@ -14307,8 +14268,8 @@
         <v>FR-01</v>
       </c>
       <c r="J109" s="4" t="str">
-        <f>D109&amp;"-"&amp;E109&amp;"-"&amp;COUNTIFS($D$2:D109,D109,$E$2:E109,E109)</f>
-        <v>Feature_Request-Routines-22</v>
+        <f>D109&amp;"-"&amp;E109&amp;"-"&amp;COUNTIFS($D$4:D109,D109,$E$4:E109,E109)</f>
+        <v>Feature_Request-Routines-21</v>
       </c>
       <c r="K109" s="1">
         <f t="shared" si="7"/>
@@ -14317,53 +14278,53 @@
     </row>
     <row r="110" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G110">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110" s="1" t="str">
         <f>IFERROR(VLOOKUP(D110&amp;"-"&amp;E110,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Routine Engine</v>
+        <v>Platform Integrations</v>
       </c>
       <c r="I110" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D110&amp;"-"&amp;E110,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>Future</v>
       </c>
       <c r="J110" s="4" t="str">
-        <f>D110&amp;"-"&amp;E110&amp;"-"&amp;COUNTIFS($D$2:D110,D110,$E$2:E110,E110)</f>
-        <v>Feature_Request-Routines-23</v>
+        <f>D110&amp;"-"&amp;E110&amp;"-"&amp;COUNTIFS($D$4:D110,D110,$E$4:E110,E110)</f>
+        <v>Integrations-Apple_Watch-5</v>
       </c>
       <c r="K110" s="1">
         <f t="shared" si="7"/>
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>7</v>
@@ -14372,11 +14333,11 @@
         <v>245</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G111">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111" s="1" t="str">
         <f>IFERROR(VLOOKUP(D111&amp;"-"&amp;E111,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
@@ -14387,8 +14348,8 @@
         <v>FR-01</v>
       </c>
       <c r="J111" s="4" t="str">
-        <f>D111&amp;"-"&amp;E111&amp;"-"&amp;COUNTIFS($D$2:D111,D111,$E$2:E111,E111)</f>
-        <v>Feature_Request-Routines-24</v>
+        <f>D111&amp;"-"&amp;E111&amp;"-"&amp;COUNTIFS($D$4:D111,D111,$E$4:E111,E111)</f>
+        <v>Feature_Request-Routines-22</v>
       </c>
       <c r="K111" s="1">
         <f t="shared" si="7"/>
@@ -14397,13 +14358,13 @@
     </row>
     <row r="112" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>7</v>
@@ -14412,11 +14373,11 @@
         <v>245</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G112">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H112" s="1" t="str">
         <f>IFERROR(VLOOKUP(D112&amp;"-"&amp;E112,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
@@ -14427,8 +14388,8 @@
         <v>FR-01</v>
       </c>
       <c r="J112" s="4" t="str">
-        <f>D112&amp;"-"&amp;E112&amp;"-"&amp;COUNTIFS($D$2:D112,D112,$E$2:E112,E112)</f>
-        <v>Feature_Request-Routines-25</v>
+        <f>D112&amp;"-"&amp;E112&amp;"-"&amp;COUNTIFS($D$4:D112,D112,$E$4:E112,E112)</f>
+        <v>Feature_Request-Routines-23</v>
       </c>
       <c r="K112" s="1">
         <f t="shared" si="7"/>
@@ -14437,59 +14398,59 @@
     </row>
     <row r="113" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G113">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H113" s="1" t="str">
         <f>IFERROR(VLOOKUP(D113&amp;"-"&amp;E113,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Support &amp; UX</v>
+        <v>Routine Engine</v>
       </c>
       <c r="I113" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D113&amp;"-"&amp;E113,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>Future</v>
+        <v>FR-01</v>
       </c>
       <c r="J113" s="4" t="str">
-        <f>D113&amp;"-"&amp;E113&amp;"-"&amp;COUNTIFS($D$2:D113,D113,$E$2:E113,E113)</f>
-        <v>Bug-Uncategorized-4</v>
+        <f>D113&amp;"-"&amp;E113&amp;"-"&amp;COUNTIFS($D$4:D113,D113,$E$4:E113,E113)</f>
+        <v>Feature_Request-Routines-24</v>
       </c>
       <c r="K113" s="1">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C114" s="5" t="s">
-        <v>236</v>
+        <v>24</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>258</v>
@@ -14500,45 +14461,128 @@
       </c>
       <c r="H114" s="1" t="str">
         <f>IFERROR(VLOOKUP(D114&amp;"-"&amp;E114,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
-        <v>Pricing &amp; Paywall</v>
+        <v>Routine Engine</v>
       </c>
       <c r="I114" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D114&amp;"-"&amp;E114,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>Future</v>
+        <v>FR-01</v>
       </c>
       <c r="J114" s="4" t="str">
-        <f>D114&amp;"-"&amp;E114&amp;"-"&amp;COUNTIFS($D$2:D114,D114,$E$2:E114,E114)</f>
-        <v>Subscription-Refund-4</v>
+        <f>D114&amp;"-"&amp;E114&amp;"-"&amp;COUNTIFS($D$4:D114,D114,$E$4:E114,E114)</f>
+        <v>Feature_Request-Routines-25</v>
       </c>
       <c r="K114" s="1">
         <f t="shared" si="7"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="G115">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H115" s="1" t="str">
+        <f>IFERROR(VLOOKUP(D115&amp;"-"&amp;E115,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
+        <v>Support &amp; UX</v>
+      </c>
+      <c r="I115" s="1" t="str">
+        <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D115&amp;"-"&amp;E115,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
+        <v>Future</v>
+      </c>
+      <c r="J115" s="4" t="str">
+        <f>D115&amp;"-"&amp;E115&amp;"-"&amp;COUNTIFS($D$4:D115,D115,$E$4:E115,E115)</f>
+        <v>Bug-Uncategorized-4</v>
+      </c>
+      <c r="K115" s="1">
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E226" s="3"/>
+    <row r="116" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G116">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="H116" s="1" t="str">
+        <f>IFERROR(VLOOKUP(D116&amp;"-"&amp;E116,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</f>
+        <v>Pricing &amp; Paywall</v>
+      </c>
+      <c r="I116" s="1" t="str">
+        <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D116&amp;"-"&amp;E116,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
+        <v>Future</v>
+      </c>
+      <c r="J116" s="4" t="str">
+        <f>D116&amp;"-"&amp;E116&amp;"-"&amp;COUNTIFS($D$4:D116,D116,$E$4:E116,E116)</f>
+        <v>Subscription-Refund-4</v>
+      </c>
+      <c r="K116" s="1">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="228" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E228" s="3"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K2"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A2:F114 H2:K114">
+  <conditionalFormatting sqref="A4:F116 H4:K116">
     <cfRule type="containsBlanks" dxfId="0" priority="1">
-      <formula>LEN(TRIM(A2))=0</formula>
+      <formula>LEN(TRIM(A4))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Theme" error="Select from dropdown only" sqref="D227:D228" xr:uid="{47A2DB2E-9038-524C-8BA0-28D1B3C3D381}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Theme" error="Select from dropdown only" sqref="D229:D230" xr:uid="{47A2DB2E-9038-524C-8BA0-28D1B3C3D381}">
       <formula1>"Bug;Feature_Request;UI;Subscription;Integrations;Performance;Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid ReqGroup" error="Select from dropdown only" sqref="H115:H227" xr:uid="{5AF90979-F149-484E-8075-B8957A5AF5F7}">
-      <formula1>$B$2:$B$118</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid ReqGroup" error="Select from dropdown only" sqref="H117:H229" xr:uid="{5AF90979-F149-484E-8075-B8957A5AF5F7}">
+      <formula1>$B$4:$B$120</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Theme" error="Select from dropdown only" sqref="D115:D226" xr:uid="{457EDCF6-D7D2-9948-AC0D-C59418782E10}">
-      <formula1>$A$2:$A$119</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Theme" error="Select from dropdown only" sqref="D117:D228" xr:uid="{457EDCF6-D7D2-9948-AC0D-C59418782E10}">
+      <formula1>$A$4:$A$121</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sub-Theme Required" error="Enter specific pain point (e.g. 'Calendar Sync Failure')" sqref="E115:E226" xr:uid="{E2C5BCC3-29C7-EB49-8A29-5A9848016060}">
-      <formula1>LEN(E115) &gt; 2</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sub-Theme Required" error="Enter specific pain point (e.g. 'Calendar Sync Failure')" sqref="E117:E228" xr:uid="{E2C5BCC3-29C7-EB49-8A29-5A9848016060}">
+      <formula1>LEN(E117) &gt; 2</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid ReqGroup" error="Select from dropdown only" sqref="H2:H114" xr:uid="{CCF67187-F131-6F42-967F-D92FA0E2FBE0}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid ReqGroup" error="Select from dropdown only" sqref="H4:H116" xr:uid="{CCF67187-F131-6F42-967F-D92FA0E2FBE0}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -14551,7 +14595,7 @@
           <x14:formula1>
             <xm:f>Analysis_Lookups!$A$3:$A$9</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D114</xm:sqref>
+          <xm:sqref>D4:D116</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Requirements-Analysis/Affinity_Traceability_Analysis_Tiimo.xlsx
+++ b/Requirements-Analysis/Affinity_Traceability_Analysis_Tiimo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chitrangidoshi/Documents/Buisness Analyst/Case Study/Tiimo/Requirement Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B1413A-B03C-594A-BBDB-68125FD955B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE9BC4D6-6ACB-1F4C-9969-964254ABA126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{A9674CC6-0D77-DC4F-B371-451AB74EFA0F}"/>
   </bookViews>
@@ -28,7 +28,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="40" r:id="rId4"/>
+    <pivotCache cacheId="9" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="322">
   <si>
     <t>Source</t>
   </si>
@@ -912,9 +912,6 @@
     <t>Future</t>
   </si>
   <si>
-    <t>SR-01</t>
-  </si>
-  <si>
     <t>Server Expansion</t>
   </si>
   <si>
@@ -976,21 +973,6 @@
   </si>
   <si>
     <t>Future Considerations</t>
-  </si>
-  <si>
-    <t>FR-01</t>
-  </si>
-  <si>
-    <t>SR-03</t>
-  </si>
-  <si>
-    <t>Routine Engine (FR-01 / SR-01)</t>
-  </si>
-  <si>
-    <t>Reliable Sync (FR-04)</t>
-  </si>
-  <si>
-    <t>Crash Prevention (NFR-03)</t>
   </si>
   <si>
     <t>(All)</t>
@@ -1056,6 +1038,24 @@
   </si>
   <si>
     <t>REQUIREMENTS AFFINITY AND TRACEABILITY TABLE - TIIMO IPHONE CHURN REDUCTION</t>
+  </si>
+  <si>
+    <t>SR-01, SR-05</t>
+  </si>
+  <si>
+    <t>FR-04, FR-05</t>
+  </si>
+  <si>
+    <t>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</t>
+  </si>
+  <si>
+    <t>SR-03, NFR-04</t>
+  </si>
+  <si>
+    <t>Req ID's</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crash Prevention </t>
   </si>
 </sst>
 </file>
@@ -1211,7 +1211,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1309,12 +1309,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1362,6 +1371,12 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1371,24 +1386,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Heading 1" xfId="1" builtinId="16"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="19">
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1398,6 +1423,53 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.749992370372631"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.749992370372631"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1593,53 +1665,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.749992370372631"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.749992370372631"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <fgColor rgb="FFB9B4FF"/>
@@ -1671,8 +1696,8 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="Affinity Analysis Table" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Affinity Analysis Table" pivot="0" count="2" xr9:uid="{A07C40A8-F901-C14E-9F2C-AF6731443204}">
-      <tableStyleElement type="wholeTable" dxfId="17"/>
-      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="wholeTable" dxfId="18"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -6144,7 +6169,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Chitrangi Doshi" refreshedDate="46099.635477777774" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="113" xr:uid="{5C47B18F-E9A7-E940-BD84-CA85D6EBF19E}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Chitrangi Doshi" refreshedDate="46100.519647685185" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="113" xr:uid="{5C47B18F-E9A7-E940-BD84-CA85D6EBF19E}">
   <cacheSource type="worksheet">
     <worksheetSource name="Table_Affinity_Analysis"/>
   </cacheSource>
@@ -6221,121 +6246,7 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Cluster_ID" numFmtId="0">
-      <sharedItems count="113">
-        <s v="Bug-Tasks-1"/>
-        <s v="Bug-Calendar-1"/>
-        <s v="Bug-UI-1"/>
-        <s v="Subscription-Refund-1"/>
-        <s v="UI-Clutter-1"/>
-        <s v="Other-Uncategorized-1"/>
-        <s v="Subscription-Paywall-1"/>
-        <s v="UI-Setup-1"/>
-        <s v="Subscription-Paywall-2"/>
-        <s v="Performance-Crash-1"/>
-        <s v="Bug-Tasks-2"/>
-        <s v="Subscription-Paywall-3"/>
-        <s v="Feature_Request-Routines-1"/>
-        <s v="Feature_Request-Routines-2"/>
-        <s v="Other-Uncategorized-2"/>
-        <s v="Other-Uncategorized-3"/>
-        <s v="UI-Uncategorized-1"/>
-        <s v="Subscription-Paywall-4"/>
-        <s v="UI-Clutter-2"/>
-        <s v="UI-Setup-2"/>
-        <s v="Feature_Request-Routines-3"/>
-        <s v="Feature_Request-Routines-4"/>
-        <s v="Subscription-Auto_Renew_Charge-1"/>
-        <s v="Feature_Request-Routines-5"/>
-        <s v="Feature_Request-Routines-6"/>
-        <s v="Subscription-Refund-2"/>
-        <s v="Feature_Request-Routines-7"/>
-        <s v="Feature_Request-Routines-8"/>
-        <s v="Bug-UI-2"/>
-        <s v="Bug-UI-3"/>
-        <s v="Performance-Crash-2"/>
-        <s v="UI-Uncategorized-2"/>
-        <s v="UI-Uncategorized-3"/>
-        <s v="Subscription-Paywall-5"/>
-        <s v="Subscription-Paywall-6"/>
-        <s v="Bug-Uncategorized-1"/>
-        <s v="UI-Clutter-3"/>
-        <s v="Bug-Notifications-1"/>
-        <s v="Bug-Calendar-2"/>
-        <s v="Bug-Calendar-3"/>
-        <s v="Bug-Uncategorized-2"/>
-        <s v="Subscription-Refund-3"/>
-        <s v="Subscription-Uncategorized-1"/>
-        <s v="Integrations-Apple_Watch-1"/>
-        <s v="Bug-Calendar-4"/>
-        <s v="Integrations-Google_Calendar-1"/>
-        <s v="Other-Uncategorized-4"/>
-        <s v="Integrations-Apple_Watch-2"/>
-        <s v="Bug-Uncategorized-3"/>
-        <s v="Integrations-Android-1"/>
-        <s v="Other-Uncategorized-5"/>
-        <s v="Feature_Request-Routines-9"/>
-        <s v="Feature_Request-Routines-10"/>
-        <s v="Feature_Request-Routines-11"/>
-        <s v="Feature_Request-Alerts-1"/>
-        <s v="Integrations-Google_Calendar-2"/>
-        <s v="Subscription-Paywall-7"/>
-        <s v="Feature_Request-Routines-12"/>
-        <s v="Feature_Request-Routines-13"/>
-        <s v="Feature_Request-Routines-14"/>
-        <s v="Bug-UI-4"/>
-        <s v="Feature_Request-Routines-15"/>
-        <s v="UI-Clutter-4"/>
-        <s v="Bug-UI-5"/>
-        <s v="Integrations-Web_Desktop-1"/>
-        <s v="Bug-UI-6"/>
-        <s v="Bug-Calendar-5"/>
-        <s v="Performance-Crash-3"/>
-        <s v="Integrations-Calendar-1"/>
-        <s v="Performance-Crash-4"/>
-        <s v="Subscription-High_Price-1"/>
-        <s v="Bug-Calendar-6"/>
-        <s v="Bug-Routines-1"/>
-        <s v="Bug-Calendar-7"/>
-        <s v="Bug-UI-7"/>
-        <s v="Performance-Crash-5"/>
-        <s v="Bug-Calendar-8"/>
-        <s v="Other-Uncategorized-6"/>
-        <s v="Subscription-High_Price-2"/>
-        <s v="Feature_Request-Routines-16"/>
-        <s v="Feature_Request-Uncategorized-1"/>
-        <s v="Other-Uncategorized-7"/>
-        <s v="Feature_Request-Routines-17"/>
-        <s v="Feature_Request-Widgets-1"/>
-        <s v="Feature_Request-Uncategorized-2"/>
-        <s v="Feature_Request-Routines-18"/>
-        <s v="Bug-AI-1"/>
-        <s v="Subscription-Paywall-8"/>
-        <s v="Subscription-Uncategorized-2"/>
-        <s v="Feature_Request-Uncategorized-3"/>
-        <s v="Integrations-Calendar-2"/>
-        <s v="Integrations-Android-2"/>
-        <s v="Integrations-Android-3"/>
-        <s v="Integrations-Android-4"/>
-        <s v="Integrations-Apple_Watch-3"/>
-        <s v="Subscription-Uncategorized-3"/>
-        <s v="Subscription-Uncategorized-4"/>
-        <s v="Feature_Request-Uncategorized-4"/>
-        <s v="Integrations-Apple_Watch-4"/>
-        <s v="Other-Uncategorized-8"/>
-        <s v="Bug-Calendar-9"/>
-        <s v="Bug-Timers-1"/>
-        <s v="Feature_Request-Routines-19"/>
-        <s v="UI-Uncategorized-4"/>
-        <s v="Feature_Request-Routines-20"/>
-        <s v="Feature_Request-Routines-21"/>
-        <s v="Integrations-Apple_Watch-5"/>
-        <s v="Feature_Request-Routines-22"/>
-        <s v="Feature_Request-Routines-23"/>
-        <s v="Feature_Request-Routines-24"/>
-        <s v="Feature_Request-Routines-25"/>
-        <s v="Bug-Uncategorized-4"/>
-        <s v="Subscription-Refund-4"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="Frequency" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="25" count="8">
@@ -6370,7 +6281,7 @@
     <x v="0"/>
     <x v="0"/>
     <s v="FR-04"/>
-    <x v="0"/>
+    <s v="Bug-Tasks-1"/>
     <x v="0"/>
   </r>
   <r>
@@ -6382,8 +6293,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
-    <s v="FR-04"/>
-    <x v="1"/>
+    <s v="FR-04, FR-05"/>
+    <s v="Bug-Calendar-1"/>
     <x v="1"/>
   </r>
   <r>
@@ -6396,7 +6307,7 @@
     <x v="0"/>
     <x v="0"/>
     <s v="FR-04"/>
-    <x v="2"/>
+    <s v="Bug-UI-1"/>
     <x v="2"/>
   </r>
   <r>
@@ -6409,7 +6320,7 @@
     <x v="1"/>
     <x v="1"/>
     <s v="Future"/>
-    <x v="3"/>
+    <s v="Subscription-Refund-1"/>
     <x v="3"/>
   </r>
   <r>
@@ -6421,8 +6332,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="2"/>
-    <s v="SR-03"/>
-    <x v="4"/>
+    <s v="SR-03, NFR-04"/>
+    <s v="UI-Clutter-1"/>
     <x v="3"/>
   </r>
   <r>
@@ -6435,7 +6346,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="5"/>
+    <s v="Other-Uncategorized-1"/>
     <x v="4"/>
   </r>
   <r>
@@ -6448,7 +6359,7 @@
     <x v="1"/>
     <x v="1"/>
     <s v="Future"/>
-    <x v="6"/>
+    <s v="Subscription-Paywall-1"/>
     <x v="4"/>
   </r>
   <r>
@@ -6460,8 +6371,8 @@
     <x v="1"/>
     <x v="1"/>
     <x v="2"/>
-    <s v="SR-01"/>
-    <x v="7"/>
+    <s v="SR-01, SR-05"/>
+    <s v="UI-Setup-1"/>
     <x v="0"/>
   </r>
   <r>
@@ -6474,7 +6385,7 @@
     <x v="0"/>
     <x v="1"/>
     <s v="Future"/>
-    <x v="8"/>
+    <s v="Subscription-Paywall-2"/>
     <x v="4"/>
   </r>
   <r>
@@ -6487,7 +6398,7 @@
     <x v="0"/>
     <x v="4"/>
     <s v="NFR-03"/>
-    <x v="9"/>
+    <s v="Performance-Crash-1"/>
     <x v="5"/>
   </r>
   <r>
@@ -6500,7 +6411,7 @@
     <x v="1"/>
     <x v="0"/>
     <s v="FR-04"/>
-    <x v="10"/>
+    <s v="Bug-Tasks-2"/>
     <x v="0"/>
   </r>
   <r>
@@ -6513,7 +6424,7 @@
     <x v="1"/>
     <x v="1"/>
     <s v="Future"/>
-    <x v="11"/>
+    <s v="Subscription-Paywall-3"/>
     <x v="4"/>
   </r>
   <r>
@@ -6525,8 +6436,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="12"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-1"/>
     <x v="6"/>
   </r>
   <r>
@@ -6538,8 +6449,8 @@
     <x v="1"/>
     <x v="1"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="13"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-2"/>
     <x v="6"/>
   </r>
   <r>
@@ -6552,7 +6463,7 @@
     <x v="1"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="14"/>
+    <s v="Other-Uncategorized-2"/>
     <x v="4"/>
   </r>
   <r>
@@ -6565,7 +6476,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="15"/>
+    <s v="Other-Uncategorized-3"/>
     <x v="4"/>
   </r>
   <r>
@@ -6578,7 +6489,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="16"/>
+    <s v="UI-Uncategorized-1"/>
     <x v="3"/>
   </r>
   <r>
@@ -6591,7 +6502,7 @@
     <x v="0"/>
     <x v="1"/>
     <s v="Future"/>
-    <x v="17"/>
+    <s v="Subscription-Paywall-4"/>
     <x v="4"/>
   </r>
   <r>
@@ -6603,8 +6514,8 @@
     <x v="1"/>
     <x v="1"/>
     <x v="2"/>
-    <s v="SR-03"/>
-    <x v="18"/>
+    <s v="SR-03, NFR-04"/>
+    <s v="UI-Clutter-2"/>
     <x v="3"/>
   </r>
   <r>
@@ -6616,8 +6527,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="2"/>
-    <s v="SR-01"/>
-    <x v="19"/>
+    <s v="SR-01, SR-05"/>
+    <s v="UI-Setup-2"/>
     <x v="0"/>
   </r>
   <r>
@@ -6629,8 +6540,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="20"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-3"/>
     <x v="6"/>
   </r>
   <r>
@@ -6642,8 +6553,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="21"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-4"/>
     <x v="6"/>
   </r>
   <r>
@@ -6656,7 +6567,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="22"/>
+    <s v="Subscription-Auto_Renew_Charge-1"/>
     <x v="7"/>
   </r>
   <r>
@@ -6668,8 +6579,8 @@
     <x v="1"/>
     <x v="1"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="23"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-5"/>
     <x v="6"/>
   </r>
   <r>
@@ -6681,8 +6592,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="24"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-6"/>
     <x v="6"/>
   </r>
   <r>
@@ -6695,7 +6606,7 @@
     <x v="1"/>
     <x v="1"/>
     <s v="Future"/>
-    <x v="25"/>
+    <s v="Subscription-Refund-2"/>
     <x v="3"/>
   </r>
   <r>
@@ -6707,8 +6618,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="26"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-7"/>
     <x v="6"/>
   </r>
   <r>
@@ -6720,8 +6631,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="27"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-8"/>
     <x v="6"/>
   </r>
   <r>
@@ -6734,7 +6645,7 @@
     <x v="0"/>
     <x v="0"/>
     <s v="FR-04"/>
-    <x v="28"/>
+    <s v="Bug-UI-2"/>
     <x v="2"/>
   </r>
   <r>
@@ -6747,7 +6658,7 @@
     <x v="0"/>
     <x v="0"/>
     <s v="FR-04"/>
-    <x v="29"/>
+    <s v="Bug-UI-3"/>
     <x v="2"/>
   </r>
   <r>
@@ -6760,7 +6671,7 @@
     <x v="1"/>
     <x v="4"/>
     <s v="NFR-03"/>
-    <x v="30"/>
+    <s v="Performance-Crash-2"/>
     <x v="5"/>
   </r>
   <r>
@@ -6773,7 +6684,7 @@
     <x v="1"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="31"/>
+    <s v="UI-Uncategorized-2"/>
     <x v="3"/>
   </r>
   <r>
@@ -6786,7 +6697,7 @@
     <x v="1"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="32"/>
+    <s v="UI-Uncategorized-3"/>
     <x v="3"/>
   </r>
   <r>
@@ -6799,7 +6710,7 @@
     <x v="1"/>
     <x v="1"/>
     <s v="Future"/>
-    <x v="33"/>
+    <s v="Subscription-Paywall-5"/>
     <x v="4"/>
   </r>
   <r>
@@ -6812,7 +6723,7 @@
     <x v="1"/>
     <x v="1"/>
     <s v="Future"/>
-    <x v="34"/>
+    <s v="Subscription-Paywall-6"/>
     <x v="4"/>
   </r>
   <r>
@@ -6825,7 +6736,7 @@
     <x v="1"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="35"/>
+    <s v="Bug-Uncategorized-1"/>
     <x v="3"/>
   </r>
   <r>
@@ -6837,8 +6748,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="2"/>
-    <s v="SR-03"/>
-    <x v="36"/>
+    <s v="SR-03, NFR-04"/>
+    <s v="UI-Clutter-3"/>
     <x v="3"/>
   </r>
   <r>
@@ -6851,7 +6762,7 @@
     <x v="1"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="37"/>
+    <s v="Bug-Notifications-1"/>
     <x v="7"/>
   </r>
   <r>
@@ -6863,8 +6774,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
-    <s v="FR-04"/>
-    <x v="38"/>
+    <s v="FR-04, FR-05"/>
+    <s v="Bug-Calendar-2"/>
     <x v="1"/>
   </r>
   <r>
@@ -6876,8 +6787,8 @@
     <x v="1"/>
     <x v="1"/>
     <x v="0"/>
-    <s v="FR-04"/>
-    <x v="39"/>
+    <s v="FR-04, FR-05"/>
+    <s v="Bug-Calendar-3"/>
     <x v="1"/>
   </r>
   <r>
@@ -6890,7 +6801,7 @@
     <x v="1"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="40"/>
+    <s v="Bug-Uncategorized-2"/>
     <x v="3"/>
   </r>
   <r>
@@ -6903,7 +6814,7 @@
     <x v="1"/>
     <x v="1"/>
     <s v="Future"/>
-    <x v="41"/>
+    <s v="Subscription-Refund-3"/>
     <x v="3"/>
   </r>
   <r>
@@ -6916,7 +6827,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="42"/>
+    <s v="Subscription-Uncategorized-1"/>
     <x v="3"/>
   </r>
   <r>
@@ -6929,7 +6840,7 @@
     <x v="0"/>
     <x v="6"/>
     <s v="Future"/>
-    <x v="43"/>
+    <s v="Integrations-Apple_Watch-1"/>
     <x v="5"/>
   </r>
   <r>
@@ -6941,8 +6852,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
-    <s v="FR-04"/>
-    <x v="44"/>
+    <s v="FR-04, FR-05"/>
+    <s v="Bug-Calendar-4"/>
     <x v="1"/>
   </r>
   <r>
@@ -6955,7 +6866,7 @@
     <x v="1"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="45"/>
+    <s v="Integrations-Google_Calendar-1"/>
     <x v="0"/>
   </r>
   <r>
@@ -6968,7 +6879,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="46"/>
+    <s v="Other-Uncategorized-4"/>
     <x v="4"/>
   </r>
   <r>
@@ -6981,7 +6892,7 @@
     <x v="0"/>
     <x v="6"/>
     <s v="Future"/>
-    <x v="47"/>
+    <s v="Integrations-Apple_Watch-2"/>
     <x v="5"/>
   </r>
   <r>
@@ -6994,7 +6905,7 @@
     <x v="1"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="48"/>
+    <s v="Bug-Uncategorized-3"/>
     <x v="3"/>
   </r>
   <r>
@@ -7007,7 +6918,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="49"/>
+    <s v="Integrations-Android-1"/>
     <x v="3"/>
   </r>
   <r>
@@ -7020,7 +6931,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="50"/>
+    <s v="Other-Uncategorized-5"/>
     <x v="4"/>
   </r>
   <r>
@@ -7032,8 +6943,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="51"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-9"/>
     <x v="6"/>
   </r>
   <r>
@@ -7045,8 +6956,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="52"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-10"/>
     <x v="6"/>
   </r>
   <r>
@@ -7058,8 +6969,8 @@
     <x v="1"/>
     <x v="1"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="53"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-11"/>
     <x v="6"/>
   </r>
   <r>
@@ -7072,7 +6983,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="54"/>
+    <s v="Feature_Request-Alerts-1"/>
     <x v="7"/>
   </r>
   <r>
@@ -7085,7 +6996,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="55"/>
+    <s v="Integrations-Google_Calendar-2"/>
     <x v="0"/>
   </r>
   <r>
@@ -7098,7 +7009,7 @@
     <x v="0"/>
     <x v="1"/>
     <s v="Future"/>
-    <x v="56"/>
+    <s v="Subscription-Paywall-7"/>
     <x v="4"/>
   </r>
   <r>
@@ -7110,8 +7021,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="57"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-12"/>
     <x v="6"/>
   </r>
   <r>
@@ -7123,8 +7034,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="58"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-13"/>
     <x v="6"/>
   </r>
   <r>
@@ -7136,8 +7047,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="59"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-14"/>
     <x v="6"/>
   </r>
   <r>
@@ -7150,7 +7061,7 @@
     <x v="1"/>
     <x v="0"/>
     <s v="FR-04"/>
-    <x v="60"/>
+    <s v="Bug-UI-4"/>
     <x v="2"/>
   </r>
   <r>
@@ -7162,8 +7073,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="61"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-15"/>
     <x v="6"/>
   </r>
   <r>
@@ -7175,8 +7086,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="2"/>
-    <s v="SR-03"/>
-    <x v="62"/>
+    <s v="SR-03, NFR-04"/>
+    <s v="UI-Clutter-4"/>
     <x v="3"/>
   </r>
   <r>
@@ -7189,7 +7100,7 @@
     <x v="1"/>
     <x v="0"/>
     <s v="FR-04"/>
-    <x v="63"/>
+    <s v="Bug-UI-5"/>
     <x v="2"/>
   </r>
   <r>
@@ -7202,7 +7113,7 @@
     <x v="1"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="64"/>
+    <s v="Integrations-Web_Desktop-1"/>
     <x v="7"/>
   </r>
   <r>
@@ -7215,7 +7126,7 @@
     <x v="1"/>
     <x v="0"/>
     <s v="FR-04"/>
-    <x v="65"/>
+    <s v="Bug-UI-6"/>
     <x v="2"/>
   </r>
   <r>
@@ -7227,8 +7138,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
-    <s v="FR-04"/>
-    <x v="66"/>
+    <s v="FR-04, FR-05"/>
+    <s v="Bug-Calendar-5"/>
     <x v="1"/>
   </r>
   <r>
@@ -7241,7 +7152,7 @@
     <x v="0"/>
     <x v="4"/>
     <s v="NFR-03"/>
-    <x v="67"/>
+    <s v="Performance-Crash-3"/>
     <x v="5"/>
   </r>
   <r>
@@ -7254,7 +7165,7 @@
     <x v="1"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="68"/>
+    <s v="Integrations-Calendar-1"/>
     <x v="0"/>
   </r>
   <r>
@@ -7267,7 +7178,7 @@
     <x v="1"/>
     <x v="4"/>
     <s v="NFR-03"/>
-    <x v="69"/>
+    <s v="Performance-Crash-4"/>
     <x v="5"/>
   </r>
   <r>
@@ -7280,7 +7191,7 @@
     <x v="1"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="70"/>
+    <s v="Subscription-High_Price-1"/>
     <x v="0"/>
   </r>
   <r>
@@ -7292,8 +7203,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
-    <s v="FR-04"/>
-    <x v="71"/>
+    <s v="FR-04, FR-05"/>
+    <s v="Bug-Calendar-6"/>
     <x v="1"/>
   </r>
   <r>
@@ -7306,7 +7217,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="72"/>
+    <s v="Bug-Routines-1"/>
     <x v="7"/>
   </r>
   <r>
@@ -7318,8 +7229,8 @@
     <x v="1"/>
     <x v="1"/>
     <x v="0"/>
-    <s v="FR-04"/>
-    <x v="73"/>
+    <s v="FR-04, FR-05"/>
+    <s v="Bug-Calendar-7"/>
     <x v="1"/>
   </r>
   <r>
@@ -7332,7 +7243,7 @@
     <x v="0"/>
     <x v="0"/>
     <s v="FR-04"/>
-    <x v="74"/>
+    <s v="Bug-UI-7"/>
     <x v="2"/>
   </r>
   <r>
@@ -7345,7 +7256,7 @@
     <x v="1"/>
     <x v="4"/>
     <s v="NFR-03"/>
-    <x v="75"/>
+    <s v="Performance-Crash-5"/>
     <x v="5"/>
   </r>
   <r>
@@ -7357,8 +7268,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
-    <s v="FR-04"/>
-    <x v="76"/>
+    <s v="FR-04, FR-05"/>
+    <s v="Bug-Calendar-8"/>
     <x v="1"/>
   </r>
   <r>
@@ -7371,7 +7282,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="77"/>
+    <s v="Other-Uncategorized-6"/>
     <x v="4"/>
   </r>
   <r>
@@ -7384,7 +7295,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="78"/>
+    <s v="Subscription-High_Price-2"/>
     <x v="0"/>
   </r>
   <r>
@@ -7396,8 +7307,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="79"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-16"/>
     <x v="6"/>
   </r>
   <r>
@@ -7410,7 +7321,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="80"/>
+    <s v="Feature_Request-Uncategorized-1"/>
     <x v="3"/>
   </r>
   <r>
@@ -7423,7 +7334,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="81"/>
+    <s v="Other-Uncategorized-7"/>
     <x v="4"/>
   </r>
   <r>
@@ -7435,8 +7346,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="82"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-17"/>
     <x v="6"/>
   </r>
   <r>
@@ -7449,7 +7360,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="83"/>
+    <s v="Feature_Request-Widgets-1"/>
     <x v="7"/>
   </r>
   <r>
@@ -7462,7 +7373,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="84"/>
+    <s v="Feature_Request-Uncategorized-2"/>
     <x v="3"/>
   </r>
   <r>
@@ -7474,8 +7385,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="85"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-18"/>
     <x v="6"/>
   </r>
   <r>
@@ -7488,7 +7399,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="86"/>
+    <s v="Bug-AI-1"/>
     <x v="7"/>
   </r>
   <r>
@@ -7501,7 +7412,7 @@
     <x v="0"/>
     <x v="1"/>
     <s v="Future"/>
-    <x v="87"/>
+    <s v="Subscription-Paywall-8"/>
     <x v="4"/>
   </r>
   <r>
@@ -7514,7 +7425,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="88"/>
+    <s v="Subscription-Uncategorized-2"/>
     <x v="3"/>
   </r>
   <r>
@@ -7527,7 +7438,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="89"/>
+    <s v="Feature_Request-Uncategorized-3"/>
     <x v="3"/>
   </r>
   <r>
@@ -7540,7 +7451,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="90"/>
+    <s v="Integrations-Calendar-2"/>
     <x v="0"/>
   </r>
   <r>
@@ -7553,7 +7464,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="91"/>
+    <s v="Integrations-Android-2"/>
     <x v="3"/>
   </r>
   <r>
@@ -7566,7 +7477,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="92"/>
+    <s v="Integrations-Android-3"/>
     <x v="3"/>
   </r>
   <r>
@@ -7579,7 +7490,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="93"/>
+    <s v="Integrations-Android-4"/>
     <x v="3"/>
   </r>
   <r>
@@ -7592,7 +7503,7 @@
     <x v="0"/>
     <x v="6"/>
     <s v="Future"/>
-    <x v="94"/>
+    <s v="Integrations-Apple_Watch-3"/>
     <x v="5"/>
   </r>
   <r>
@@ -7605,7 +7516,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="95"/>
+    <s v="Subscription-Uncategorized-3"/>
     <x v="3"/>
   </r>
   <r>
@@ -7618,7 +7529,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="96"/>
+    <s v="Subscription-Uncategorized-4"/>
     <x v="3"/>
   </r>
   <r>
@@ -7631,7 +7542,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="97"/>
+    <s v="Feature_Request-Uncategorized-4"/>
     <x v="3"/>
   </r>
   <r>
@@ -7644,7 +7555,7 @@
     <x v="0"/>
     <x v="6"/>
     <s v="Future"/>
-    <x v="98"/>
+    <s v="Integrations-Apple_Watch-4"/>
     <x v="5"/>
   </r>
   <r>
@@ -7657,7 +7568,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="99"/>
+    <s v="Other-Uncategorized-8"/>
     <x v="4"/>
   </r>
   <r>
@@ -7669,8 +7580,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
-    <s v="FR-04"/>
-    <x v="100"/>
+    <s v="FR-04, FR-05"/>
+    <s v="Bug-Calendar-9"/>
     <x v="1"/>
   </r>
   <r>
@@ -7683,7 +7594,7 @@
     <x v="1"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="101"/>
+    <s v="Bug-Timers-1"/>
     <x v="7"/>
   </r>
   <r>
@@ -7695,8 +7606,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="102"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-19"/>
     <x v="6"/>
   </r>
   <r>
@@ -7709,7 +7620,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="103"/>
+    <s v="UI-Uncategorized-4"/>
     <x v="3"/>
   </r>
   <r>
@@ -7721,8 +7632,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="104"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-20"/>
     <x v="6"/>
   </r>
   <r>
@@ -7734,8 +7645,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="105"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-21"/>
     <x v="6"/>
   </r>
   <r>
@@ -7748,7 +7659,7 @@
     <x v="1"/>
     <x v="6"/>
     <s v="Future"/>
-    <x v="106"/>
+    <s v="Integrations-Apple_Watch-5"/>
     <x v="5"/>
   </r>
   <r>
@@ -7760,8 +7671,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="107"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-22"/>
     <x v="6"/>
   </r>
   <r>
@@ -7773,8 +7684,8 @@
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="108"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-23"/>
     <x v="6"/>
   </r>
   <r>
@@ -7786,8 +7697,8 @@
     <x v="1"/>
     <x v="1"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="109"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-24"/>
     <x v="6"/>
   </r>
   <r>
@@ -7799,8 +7710,8 @@
     <x v="1"/>
     <x v="1"/>
     <x v="5"/>
-    <s v="FR-01"/>
-    <x v="110"/>
+    <s v="FR-01, SR-01, FR-02, FR-03, FR-06, FR-07"/>
+    <s v="Feature_Request-Routines-25"/>
     <x v="6"/>
   </r>
   <r>
@@ -7813,7 +7724,7 @@
     <x v="0"/>
     <x v="3"/>
     <s v="Future"/>
-    <x v="111"/>
+    <s v="Bug-Uncategorized-4"/>
     <x v="3"/>
   </r>
   <r>
@@ -7826,14 +7737,941 @@
     <x v="1"/>
     <x v="1"/>
     <s v="Future"/>
-    <x v="112"/>
+    <s v="Subscription-Refund-4"/>
     <x v="3"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C49BA34E-92BB-5D4D-811E-C3031738A9DF}" name="PivotTable5" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{52AB4ED5-C7E0-8B4F-9714-5AD1125F1803}" name="PivotTable3" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
+  <location ref="A131:B145" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="11">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="8">
+        <item x="0"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="22">
+        <item x="19"/>
+        <item x="15"/>
+        <item x="14"/>
+        <item x="12"/>
+        <item x="10"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="13"/>
+        <item x="17"/>
+        <item x="11"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="20"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="18"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="9">
+        <item h="1" x="7"/>
+        <item h="1" x="0"/>
+        <item h="1" x="3"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="3"/>
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="6" hier="-1"/>
+    <pageField fld="10" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Review_Frequency" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="42">
+    <chartFormat chart="8" format="21" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="22" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="23" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="24" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="25" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="26" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="27" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="28" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="29" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="30" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="31" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="32" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="33" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="12"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="34" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="35" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="14"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="36" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="15"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="37" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="16"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="38" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="17"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="39" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="18"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="40" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="19"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="41" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="20"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="42" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="43" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="44" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="45" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="46" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="47" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="48" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="49" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="50" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="51" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="52" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="53" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="54" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="12"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="55" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="56" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="14"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="57" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="15"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="58" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="16"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="59" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="17"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="60" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="18"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="61" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="19"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="62" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="20"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D92E3B1F-A9C2-5F47-954E-BEC4DF1471DC}" name="PivotTable4" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="A51:K59" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="11">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="8">
+        <item x="0"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="22">
+        <item x="19"/>
+        <item x="15"/>
+        <item x="14"/>
+        <item x="12"/>
+        <item x="10"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="13"/>
+        <item x="17"/>
+        <item x="11"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="20"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="18"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="9">
+        <item h="1" x="7"/>
+        <item h="1" x="0"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="4"/>
+  </colFields>
+  <colItems count="10">
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="10" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Count of Review_Id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <conditionalFormats count="1">
+    <conditionalFormat scope="data" priority="1">
+      <pivotAreas count="1">
+        <pivotArea outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
+  <chartFormats count="21">
+    <chartFormat chart="8" format="21" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="22" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="23" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="24" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="25" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="26" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="27" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="28" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="29" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="30" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="31" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="32" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="33" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="12"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="34" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="35" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="14"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="36" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="15"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="37" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="16"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="38" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="17"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="39" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="18"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="40" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="19"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="41" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1" selected="0">
+            <x v="20"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C49BA34E-92BB-5D4D-811E-C3031738A9DF}" name="PivotTable5" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="A84:J121" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField dataField="1" showAll="0"/>
@@ -8504,933 +9342,6 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{52AB4ED5-C7E0-8B4F-9714-5AD1125F1803}" name="PivotTable3" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
-  <location ref="A131:B145" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="11">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="8">
-        <item x="0"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="22">
-        <item x="19"/>
-        <item x="15"/>
-        <item x="14"/>
-        <item x="12"/>
-        <item x="10"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item x="13"/>
-        <item x="17"/>
-        <item x="11"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="20"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="16"/>
-        <item x="18"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="9">
-        <item h="1" x="7"/>
-        <item h="1" x="0"/>
-        <item h="1" x="3"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="3"/>
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="6" hier="-1"/>
-    <pageField fld="10" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Review_Frequency" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="42">
-    <chartFormat chart="8" format="21" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="22" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="23" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="24" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="25" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="26" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="27" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="28" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="29" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="8"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="30" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="9"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="31" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="10"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="32" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="11"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="33" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="12"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="34" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="35" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="14"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="36" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="15"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="37" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="16"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="38" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="17"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="39" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="18"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="40" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="19"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="41" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="20"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="42" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="43" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="44" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="45" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="46" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="47" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="48" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="49" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="50" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="8"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="51" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="9"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="52" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="10"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="53" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="11"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="54" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="12"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="55" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="56" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="14"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="57" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="15"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="58" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="16"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="59" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="17"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="60" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="18"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="61" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="19"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="62" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="20"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D92E3B1F-A9C2-5F47-954E-BEC4DF1471DC}" name="PivotTable4" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="A51:K59" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="11">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="8">
-        <item x="0"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="22">
-        <item x="19"/>
-        <item x="15"/>
-        <item x="14"/>
-        <item x="12"/>
-        <item x="10"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item x="13"/>
-        <item x="17"/>
-        <item x="11"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="20"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="16"/>
-        <item x="18"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="9">
-        <item h="1" x="7"/>
-        <item h="1" x="0"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="4"/>
-  </colFields>
-  <colItems count="10">
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="10" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Count of Review_Id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <conditionalFormats count="1">
-    <conditionalFormat scope="data" priority="1">
-      <pivotAreas count="1">
-        <pivotArea outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-  </conditionalFormats>
-  <chartFormats count="21">
-    <chartFormat chart="8" format="21" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="22" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="23" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="24" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="25" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="26" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="27" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="28" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="29" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="8"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="30" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="9"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="31" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="10"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="32" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="11"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="33" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="12"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="34" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="35" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="14"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="36" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="15"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="37" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="16"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="38" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="17"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="39" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="18"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="40" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="19"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="41" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1" selected="0">
-            <x v="20"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Theme" xr10:uid="{1EF09F50-A2BC-AC4E-B60B-9F814FD478FB}" sourceName="Theme">
   <pivotTables>
@@ -9534,28 +9445,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3671B8E3-831C-2944-92F7-2BA71D57EBB5}" name="Table_Affinity_Analysis" displayName="Table_Affinity_Analysis" ref="A3:K116" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12" headerRowCellStyle="Heading 1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3671B8E3-831C-2944-92F7-2BA71D57EBB5}" name="Table_Affinity_Analysis" displayName="Table_Affinity_Analysis" ref="A3:K116" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" headerRowCellStyle="Heading 1">
   <autoFilter ref="A3:K116" xr:uid="{3671B8E3-831C-2944-92F7-2BA71D57EBB5}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{D8B7633B-220A-7845-A647-D85993E95A37}" name="Review_Id" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{19086F0C-CE61-CC49-8DCF-68D95499EB1C}" name="Source" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{93741217-0369-CD41-B32D-928B917ABD56}" name="Raw_Review_Text" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{655630C9-6872-2648-B4C4-EF46DC8C63FC}" name="Theme" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{83274B5D-B1A2-9C43-83B1-217689641447}" name="Sub_Theme" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{5012791F-CC7B-A14E-B6F8-C210EEA0E819}" name="Churn_Signal" dataDxfId="6"/>
-    <tableColumn id="19" xr3:uid="{62935A5E-A60E-0B48-82CA-010C5F46E946}" name="Churn_Flag" dataDxfId="5">
+    <tableColumn id="1" xr3:uid="{D8B7633B-220A-7845-A647-D85993E95A37}" name="Review_Id" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{19086F0C-CE61-CC49-8DCF-68D95499EB1C}" name="Source" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{93741217-0369-CD41-B32D-928B917ABD56}" name="Raw_Review_Text" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{655630C9-6872-2648-B4C4-EF46DC8C63FC}" name="Theme" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{83274B5D-B1A2-9C43-83B1-217689641447}" name="Sub_Theme" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{5012791F-CC7B-A14E-B6F8-C210EEA0E819}" name="Churn_Signal" dataDxfId="9"/>
+    <tableColumn id="19" xr3:uid="{62935A5E-A60E-0B48-82CA-010C5F46E946}" name="Churn_Flag" dataDxfId="8">
       <calculatedColumnFormula>IF(F4="yes",1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B4E101EC-A34B-CD4A-A1D9-FDE5F14F1FDE}" name="Req_Group" dataDxfId="4">
+    <tableColumn id="8" xr3:uid="{B4E101EC-A34B-CD4A-A1D9-FDE5F14F1FDE}" name="Req_Group" dataDxfId="7">
       <calculatedColumnFormula>IFERROR(VLOOKUP(D4&amp;"-"&amp;E4,Analysis_Lookups!$C$2:$D$13,2,FALSE),"Support &amp; UX")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{340D3186-319B-9E4A-84B9-ABD58EF87C52}" name="Req_ID" dataDxfId="3">
+    <tableColumn id="9" xr3:uid="{340D3186-319B-9E4A-84B9-ABD58EF87C52}" name="Req_ID" dataDxfId="6">
       <calculatedColumnFormula>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D4&amp;"-"&amp;E4,Analysis_Lookups!$C$3:$C$13,0)),"Future")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{7BF352CD-BF3A-4E4A-B382-313CC620984A}" name="Cluster_ID" dataDxfId="2">
+    <tableColumn id="11" xr3:uid="{7BF352CD-BF3A-4E4A-B382-313CC620984A}" name="Cluster_ID" dataDxfId="5">
       <calculatedColumnFormula>D4&amp;"-"&amp;E4&amp;"-"&amp;COUNTIFS($D$4:D4,D4,$E$4:E4,E4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{D6984204-8DF0-E74A-B5F0-AC89A2DE0C93}" name="Frequency" dataDxfId="1">
+    <tableColumn id="12" xr3:uid="{D6984204-8DF0-E74A-B5F0-AC89A2DE0C93}" name="Frequency" dataDxfId="4">
       <calculatedColumnFormula>COUNTIFS($D$4:$D$227,D4,$E$4:$E$227,E4)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9564,7 +9475,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{8BCD8680-DD18-9346-8156-4576C2AEE536}" name="Table2479" displayName="Table2479" ref="C9:E15" totalsRowShown="0" headerRowDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{8BCD8680-DD18-9346-8156-4576C2AEE536}" name="Table2479" displayName="Table2479" ref="C9:E15" totalsRowShown="0" headerRowDxfId="3">
   <autoFilter ref="C9:E15" xr:uid="{8BCD8680-DD18-9346-8156-4576C2AEE536}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{DCBD08E8-6984-5C42-B9B7-1AB529872030}" name="Theme-Sub_Theme"/>
@@ -9576,12 +9487,13 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{EDB269F5-078B-6748-A0EC-C7DF18A8232A}" name="Table5810" displayName="Table5810" ref="H9:J13" totalsRowShown="0" headerRowDxfId="14">
-  <autoFilter ref="H9:J13" xr:uid="{EDB269F5-078B-6748-A0EC-C7DF18A8232A}"/>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{EDB269F5-078B-6748-A0EC-C7DF18A8232A}" name="Table5810" displayName="Table5810" ref="H9:K13" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="H9:K13" xr:uid="{EDB269F5-078B-6748-A0EC-C7DF18A8232A}"/>
+  <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{4684E164-14A9-834A-949B-A280DB0A5DE3}" name="ReqGroup"/>
     <tableColumn id="2" xr3:uid="{A43C89C2-EC06-CE46-875B-5DBCBC4731DF}" name="Frequency"/>
     <tableColumn id="3" xr3:uid="{3FE9BAC7-4497-9249-ADA8-1D73E3DAD249}" name="Coverage"/>
+    <tableColumn id="4" xr3:uid="{5F565A0C-1AA4-8749-BD65-74112A580DCC}" name="Req ID's" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Affinity Analysis Table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9922,32 +9834,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28" t="s">
-        <v>321</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
+      <c r="A1" s="25" t="s">
+        <v>315</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
     </row>
     <row r="2" spans="1:22" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="31"/>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
     </row>
     <row r="3" spans="1:22" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -9969,7 +9881,7 @@
         <v>276</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>277</v>
@@ -10061,7 +9973,7 @@
       </c>
       <c r="I5" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D5&amp;"-"&amp;E5,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-04</v>
+        <v>FR-04, FR-05</v>
       </c>
       <c r="J5" s="4" t="str">
         <f>D5&amp;"-"&amp;E5&amp;"-"&amp;COUNTIFS($D$4:D5,D5,$E$4:E5,E5)</f>
@@ -10193,7 +10105,7 @@
       </c>
       <c r="I8" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D8&amp;"-"&amp;E8,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>SR-03</v>
+        <v>SR-03, NFR-04</v>
       </c>
       <c r="J8" s="4" t="str">
         <f>D8&amp;"-"&amp;E8&amp;"-"&amp;COUNTIFS($D$4:D8,D8,$E$4:E8,E8)</f>
@@ -10325,7 +10237,7 @@
       </c>
       <c r="I11" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D11&amp;"-"&amp;E11,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>SR-01</v>
+        <v>SR-01, SR-05</v>
       </c>
       <c r="J11" s="4" t="str">
         <f>D11&amp;"-"&amp;E11&amp;"-"&amp;COUNTIFS($D$4:D11,D11,$E$4:E11,E11)</f>
@@ -10545,7 +10457,7 @@
       </c>
       <c r="I16" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D16&amp;"-"&amp;E16,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J16" s="4" t="str">
         <f>D16&amp;"-"&amp;E16&amp;"-"&amp;COUNTIFS($D$4:D16,D16,$E$4:E16,E16)</f>
@@ -10585,7 +10497,7 @@
       </c>
       <c r="I17" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D17&amp;"-"&amp;E17,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J17" s="4" t="str">
         <f>D17&amp;"-"&amp;E17&amp;"-"&amp;COUNTIFS($D$4:D17,D17,$E$4:E17,E17)</f>
@@ -10785,7 +10697,7 @@
       </c>
       <c r="I22" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D22&amp;"-"&amp;E22,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>SR-03</v>
+        <v>SR-03, NFR-04</v>
       </c>
       <c r="J22" s="4" t="str">
         <f>D22&amp;"-"&amp;E22&amp;"-"&amp;COUNTIFS($D$4:D22,D22,$E$4:E22,E22)</f>
@@ -10825,7 +10737,7 @@
       </c>
       <c r="I23" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D23&amp;"-"&amp;E23,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>SR-01</v>
+        <v>SR-01, SR-05</v>
       </c>
       <c r="J23" s="4" t="str">
         <f>D23&amp;"-"&amp;E23&amp;"-"&amp;COUNTIFS($D$4:D23,D23,$E$4:E23,E23)</f>
@@ -10865,7 +10777,7 @@
       </c>
       <c r="I24" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D24&amp;"-"&amp;E24,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J24" s="4" t="str">
         <f>D24&amp;"-"&amp;E24&amp;"-"&amp;COUNTIFS($D$4:D24,D24,$E$4:E24,E24)</f>
@@ -10905,7 +10817,7 @@
       </c>
       <c r="I25" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D25&amp;"-"&amp;E25,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J25" s="4" t="str">
         <f>D25&amp;"-"&amp;E25&amp;"-"&amp;COUNTIFS($D$4:D25,D25,$E$4:E25,E25)</f>
@@ -10985,7 +10897,7 @@
       </c>
       <c r="I27" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D27&amp;"-"&amp;E27,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J27" s="4" t="str">
         <f>D27&amp;"-"&amp;E27&amp;"-"&amp;COUNTIFS($D$4:D27,D27,$E$4:E27,E27)</f>
@@ -11025,7 +10937,7 @@
       </c>
       <c r="I28" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D28&amp;"-"&amp;E28,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J28" s="4" t="str">
         <f>D28&amp;"-"&amp;E28&amp;"-"&amp;COUNTIFS($D$4:D28,D28,$E$4:E28,E28)</f>
@@ -11105,7 +11017,7 @@
       </c>
       <c r="I30" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D30&amp;"-"&amp;E30,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J30" s="4" t="str">
         <f>D30&amp;"-"&amp;E30&amp;"-"&amp;COUNTIFS($D$4:D30,D30,$E$4:E30,E30)</f>
@@ -11145,7 +11057,7 @@
       </c>
       <c r="I31" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D31&amp;"-"&amp;E31,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J31" s="4" t="str">
         <f>D31&amp;"-"&amp;E31&amp;"-"&amp;COUNTIFS($D$4:D31,D31,$E$4:E31,E31)</f>
@@ -11505,7 +11417,7 @@
       </c>
       <c r="I40" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D40&amp;"-"&amp;E40,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>SR-03</v>
+        <v>SR-03, NFR-04</v>
       </c>
       <c r="J40" s="4" t="str">
         <f>D40&amp;"-"&amp;E40&amp;"-"&amp;COUNTIFS($D$4:D40,D40,$E$4:E40,E40)</f>
@@ -11585,7 +11497,7 @@
       </c>
       <c r="I42" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D42&amp;"-"&amp;E42,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-04</v>
+        <v>FR-04, FR-05</v>
       </c>
       <c r="J42" s="4" t="str">
         <f>D42&amp;"-"&amp;E42&amp;"-"&amp;COUNTIFS($D$4:D42,D42,$E$4:E42,E42)</f>
@@ -11625,7 +11537,7 @@
       </c>
       <c r="I43" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D43&amp;"-"&amp;E43,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-04</v>
+        <v>FR-04, FR-05</v>
       </c>
       <c r="J43" s="4" t="str">
         <f>D43&amp;"-"&amp;E43&amp;"-"&amp;COUNTIFS($D$4:D43,D43,$E$4:E43,E43)</f>
@@ -11825,7 +11737,7 @@
       </c>
       <c r="I48" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D48&amp;"-"&amp;E48,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-04</v>
+        <v>FR-04, FR-05</v>
       </c>
       <c r="J48" s="4" t="str">
         <f>D48&amp;"-"&amp;E48&amp;"-"&amp;COUNTIFS($D$4:D48,D48,$E$4:E48,E48)</f>
@@ -12105,7 +12017,7 @@
       </c>
       <c r="I55" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D55&amp;"-"&amp;E55,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J55" s="4" t="str">
         <f>D55&amp;"-"&amp;E55&amp;"-"&amp;COUNTIFS($D$4:D55,D55,$E$4:E55,E55)</f>
@@ -12145,7 +12057,7 @@
       </c>
       <c r="I56" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D56&amp;"-"&amp;E56,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J56" s="4" t="str">
         <f>D56&amp;"-"&amp;E56&amp;"-"&amp;COUNTIFS($D$4:D56,D56,$E$4:E56,E56)</f>
@@ -12185,7 +12097,7 @@
       </c>
       <c r="I57" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D57&amp;"-"&amp;E57,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J57" s="4" t="str">
         <f>D57&amp;"-"&amp;E57&amp;"-"&amp;COUNTIFS($D$4:D57,D57,$E$4:E57,E57)</f>
@@ -12345,7 +12257,7 @@
       </c>
       <c r="I61" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D61&amp;"-"&amp;E61,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J61" s="4" t="str">
         <f>D61&amp;"-"&amp;E61&amp;"-"&amp;COUNTIFS($D$4:D61,D61,$E$4:E61,E61)</f>
@@ -12385,7 +12297,7 @@
       </c>
       <c r="I62" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D62&amp;"-"&amp;E62,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J62" s="4" t="str">
         <f>D62&amp;"-"&amp;E62&amp;"-"&amp;COUNTIFS($D$4:D62,D62,$E$4:E62,E62)</f>
@@ -12425,7 +12337,7 @@
       </c>
       <c r="I63" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D63&amp;"-"&amp;E63,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J63" s="4" t="str">
         <f>D63&amp;"-"&amp;E63&amp;"-"&amp;COUNTIFS($D$4:D63,D63,$E$4:E63,E63)</f>
@@ -12505,7 +12417,7 @@
       </c>
       <c r="I65" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D65&amp;"-"&amp;E65,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J65" s="4" t="str">
         <f>D65&amp;"-"&amp;E65&amp;"-"&amp;COUNTIFS($D$4:D65,D65,$E$4:E65,E65)</f>
@@ -12545,7 +12457,7 @@
       </c>
       <c r="I66" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D66&amp;"-"&amp;E66,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>SR-03</v>
+        <v>SR-03, NFR-04</v>
       </c>
       <c r="J66" s="4" t="str">
         <f>D66&amp;"-"&amp;E66&amp;"-"&amp;COUNTIFS($D$4:D66,D66,$E$4:E66,E66)</f>
@@ -12705,7 +12617,7 @@
       </c>
       <c r="I70" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D70&amp;"-"&amp;E70,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-04</v>
+        <v>FR-04, FR-05</v>
       </c>
       <c r="J70" s="4" t="str">
         <f>D70&amp;"-"&amp;E70&amp;"-"&amp;COUNTIFS($D$4:D70,D70,$E$4:E70,E70)</f>
@@ -12905,7 +12817,7 @@
       </c>
       <c r="I75" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D75&amp;"-"&amp;E75,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-04</v>
+        <v>FR-04, FR-05</v>
       </c>
       <c r="J75" s="4" t="str">
         <f>D75&amp;"-"&amp;E75&amp;"-"&amp;COUNTIFS($D$4:D75,D75,$E$4:E75,E75)</f>
@@ -12985,7 +12897,7 @@
       </c>
       <c r="I77" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D77&amp;"-"&amp;E77,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-04</v>
+        <v>FR-04, FR-05</v>
       </c>
       <c r="J77" s="4" t="str">
         <f>D77&amp;"-"&amp;E77&amp;"-"&amp;COUNTIFS($D$4:D77,D77,$E$4:E77,E77)</f>
@@ -13105,7 +13017,7 @@
       </c>
       <c r="I80" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D80&amp;"-"&amp;E80,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-04</v>
+        <v>FR-04, FR-05</v>
       </c>
       <c r="J80" s="4" t="str">
         <f>D80&amp;"-"&amp;E80&amp;"-"&amp;COUNTIFS($D$4:D80,D80,$E$4:E80,E80)</f>
@@ -13225,7 +13137,7 @@
       </c>
       <c r="I83" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D83&amp;"-"&amp;E83,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J83" s="4" t="str">
         <f>D83&amp;"-"&amp;E83&amp;"-"&amp;COUNTIFS($D$4:D83,D83,$E$4:E83,E83)</f>
@@ -13345,7 +13257,7 @@
       </c>
       <c r="I86" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D86&amp;"-"&amp;E86,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J86" s="4" t="str">
         <f>D86&amp;"-"&amp;E86&amp;"-"&amp;COUNTIFS($D$4:D86,D86,$E$4:E86,E86)</f>
@@ -13465,7 +13377,7 @@
       </c>
       <c r="I89" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D89&amp;"-"&amp;E89,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J89" s="4" t="str">
         <f>D89&amp;"-"&amp;E89&amp;"-"&amp;COUNTIFS($D$4:D89,D89,$E$4:E89,E89)</f>
@@ -14065,7 +13977,7 @@
       </c>
       <c r="I104" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D104&amp;"-"&amp;E104,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-04</v>
+        <v>FR-04, FR-05</v>
       </c>
       <c r="J104" s="4" t="str">
         <f>D104&amp;"-"&amp;E104&amp;"-"&amp;COUNTIFS($D$4:D104,D104,$E$4:E104,E104)</f>
@@ -14145,7 +14057,7 @@
       </c>
       <c r="I106" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D106&amp;"-"&amp;E106,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J106" s="4" t="str">
         <f>D106&amp;"-"&amp;E106&amp;"-"&amp;COUNTIFS($D$4:D106,D106,$E$4:E106,E106)</f>
@@ -14225,7 +14137,7 @@
       </c>
       <c r="I108" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D108&amp;"-"&amp;E108,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J108" s="4" t="str">
         <f>D108&amp;"-"&amp;E108&amp;"-"&amp;COUNTIFS($D$4:D108,D108,$E$4:E108,E108)</f>
@@ -14265,7 +14177,7 @@
       </c>
       <c r="I109" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D109&amp;"-"&amp;E109,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J109" s="4" t="str">
         <f>D109&amp;"-"&amp;E109&amp;"-"&amp;COUNTIFS($D$4:D109,D109,$E$4:E109,E109)</f>
@@ -14345,7 +14257,7 @@
       </c>
       <c r="I111" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D111&amp;"-"&amp;E111,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J111" s="4" t="str">
         <f>D111&amp;"-"&amp;E111&amp;"-"&amp;COUNTIFS($D$4:D111,D111,$E$4:E111,E111)</f>
@@ -14385,7 +14297,7 @@
       </c>
       <c r="I112" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D112&amp;"-"&amp;E112,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J112" s="4" t="str">
         <f>D112&amp;"-"&amp;E112&amp;"-"&amp;COUNTIFS($D$4:D112,D112,$E$4:E112,E112)</f>
@@ -14425,7 +14337,7 @@
       </c>
       <c r="I113" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D113&amp;"-"&amp;E113,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J113" s="4" t="str">
         <f>D113&amp;"-"&amp;E113&amp;"-"&amp;COUNTIFS($D$4:D113,D113,$E$4:E113,E113)</f>
@@ -14465,7 +14377,7 @@
       </c>
       <c r="I114" s="1" t="str">
         <f>IFERROR(INDEX(Analysis_Lookups!$E$3:$E$13,MATCH(D114&amp;"-"&amp;E114,Analysis_Lookups!$C$3:$C$13,0)),"Future")</f>
-        <v>FR-01</v>
+        <v>FR-01, SR-01, FR-02, FR-03, FR-06, FR-07</v>
       </c>
       <c r="J114" s="4" t="str">
         <f>D114&amp;"-"&amp;E114&amp;"-"&amp;COUNTIFS($D$4:D114,D114,$E$4:E114,E114)</f>
@@ -14565,7 +14477,7 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A4:F116 H4:K116">
-    <cfRule type="containsBlanks" dxfId="0" priority="1">
+    <cfRule type="containsBlanks" dxfId="1" priority="1">
       <formula>LEN(TRIM(A4))=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14616,9 +14528,9 @@
     <col min="6" max="6" width="24.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.33203125" customWidth="1"/>
     <col min="10" max="10" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.5" customWidth="1"/>
     <col min="12" max="12" width="20.83203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="28.6640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="21.83203125" bestFit="1" customWidth="1"/>
@@ -14634,74 +14546,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
-        <v>288</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
+      <c r="A1" s="27" t="s">
+        <v>287</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
     </row>
     <row r="5" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="33"/>
+    </row>
+    <row r="6" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+    </row>
+    <row r="7" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="28" t="s">
         <v>295</v>
       </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-    </row>
-    <row r="6" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-    </row>
-    <row r="7" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C7" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="H7" s="26" t="s">
-        <v>302</v>
-      </c>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="H7" s="34" t="s">
+        <v>301</v>
+      </c>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
     </row>
     <row r="8" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="28"/>
     </row>
     <row r="9" spans="1:14" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C9" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="E9" s="21" t="s">
         <v>297</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>301</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>298</v>
       </c>
       <c r="H9" s="21" t="s">
         <v>2</v>
@@ -14710,12 +14626,15 @@
         <v>4</v>
       </c>
       <c r="J9" s="21" t="s">
-        <v>303</v>
+        <v>302</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D10">
         <v>25</v>
@@ -14724,13 +14643,16 @@
         <v>0.13500000000000001</v>
       </c>
       <c r="H10" t="s">
-        <v>307</v>
+        <v>13</v>
       </c>
       <c r="I10">
         <v>25</v>
       </c>
       <c r="J10" s="14">
         <v>0.22</v>
+      </c>
+      <c r="K10" s="36" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -14744,13 +14666,16 @@
         <v>0.108</v>
       </c>
       <c r="H11" t="s">
-        <v>308</v>
+        <v>14</v>
       </c>
       <c r="I11">
         <v>18</v>
       </c>
       <c r="J11" s="14">
         <v>0.16</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -14764,13 +14689,16 @@
         <v>0.108</v>
       </c>
       <c r="H12" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="I12">
         <v>5</v>
       </c>
       <c r="J12" s="14">
         <v>0.04</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -14784,13 +14712,16 @@
         <v>8.1000000000000003E-2</v>
       </c>
       <c r="H13" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I13">
         <v>65</v>
       </c>
       <c r="J13" s="14">
         <v>0.57999999999999996</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -14806,7 +14737,7 @@
     </row>
     <row r="15" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D15">
         <v>5</v>
@@ -14821,34 +14752,34 @@
       <c r="M46" s="17"/>
     </row>
     <row r="47" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="26" t="s">
-        <v>319</v>
-      </c>
-      <c r="B47" s="26"/>
-      <c r="C47" s="26"/>
-      <c r="D47" s="26"/>
-      <c r="E47" s="26"/>
-      <c r="F47" s="26"/>
-      <c r="G47" s="26"/>
-      <c r="H47" s="26"/>
-      <c r="I47" s="26"/>
-      <c r="J47" s="26"/>
-      <c r="K47" s="26"/>
+      <c r="A47" s="28" t="s">
+        <v>313</v>
+      </c>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="28"/>
+      <c r="J47" s="28"/>
+      <c r="K47" s="28"/>
       <c r="L47" s="19"/>
       <c r="M47" s="17"/>
     </row>
     <row r="48" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="26"/>
-      <c r="B48" s="26"/>
-      <c r="C48" s="26"/>
-      <c r="D48" s="26"/>
-      <c r="E48" s="26"/>
-      <c r="F48" s="26"/>
-      <c r="G48" s="26"/>
-      <c r="H48" s="26"/>
-      <c r="I48" s="26"/>
-      <c r="J48" s="26"/>
-      <c r="K48" s="26"/>
+      <c r="A48" s="28"/>
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="28"/>
+      <c r="I48" s="28"/>
+      <c r="J48" s="28"/>
+      <c r="K48" s="28"/>
       <c r="L48" s="19"/>
       <c r="M48" s="17"/>
     </row>
@@ -14857,7 +14788,7 @@
         <v>4</v>
       </c>
       <c r="B49" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="L49" s="20"/>
       <c r="M49" s="17"/>
@@ -14867,15 +14798,15 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51" s="9" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B52" t="s">
         <v>250</v>
@@ -14912,13 +14843,20 @@
       <c r="A53" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D53">
+      <c r="B53" s="32"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="32">
         <v>9</v>
       </c>
-      <c r="J53">
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="32"/>
+      <c r="I53" s="32"/>
+      <c r="J53" s="32">
         <v>7</v>
       </c>
-      <c r="K53">
+      <c r="K53" s="32">
         <v>4</v>
       </c>
     </row>
@@ -14926,10 +14864,18 @@
       <c r="A54" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I54">
+      <c r="B54" s="32"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="32"/>
+      <c r="E54" s="32"/>
+      <c r="F54" s="32"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="32"/>
+      <c r="I54" s="32">
         <v>25</v>
       </c>
-      <c r="K54">
+      <c r="J54" s="32"/>
+      <c r="K54" s="32">
         <v>4</v>
       </c>
     </row>
@@ -14937,18 +14883,35 @@
       <c r="A55" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="32">
         <v>4</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="32">
         <v>5</v>
       </c>
+      <c r="D55" s="32"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
+      <c r="I55" s="32"/>
+      <c r="J55" s="32"/>
+      <c r="K55" s="32"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="K56">
+      <c r="B56" s="32"/>
+      <c r="C56" s="32"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="32"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="32"/>
+      <c r="I56" s="32"/>
+      <c r="J56" s="32"/>
+      <c r="K56" s="32">
         <v>8</v>
       </c>
     </row>
@@ -14956,21 +14919,37 @@
       <c r="A57" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F57">
+      <c r="B57" s="32"/>
+      <c r="C57" s="32"/>
+      <c r="D57" s="32"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32">
         <v>5</v>
       </c>
+      <c r="G57" s="32"/>
+      <c r="H57" s="32"/>
+      <c r="I57" s="32"/>
+      <c r="J57" s="32"/>
+      <c r="K57" s="32"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G58">
+      <c r="B58" s="32"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="32">
         <v>8</v>
       </c>
-      <c r="H58">
+      <c r="H58" s="32">
         <v>4</v>
       </c>
-      <c r="K58">
+      <c r="I58" s="32"/>
+      <c r="J58" s="32"/>
+      <c r="K58" s="32">
         <v>4</v>
       </c>
     </row>
@@ -14978,10 +14957,18 @@
       <c r="A59" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E59">
+      <c r="B59" s="32"/>
+      <c r="C59" s="32"/>
+      <c r="D59" s="32"/>
+      <c r="E59" s="32">
         <v>4</v>
       </c>
-      <c r="K59">
+      <c r="F59" s="32"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="32"/>
+      <c r="I59" s="32"/>
+      <c r="J59" s="32"/>
+      <c r="K59" s="32">
         <v>4</v>
       </c>
     </row>
@@ -15032,7 +15019,7 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B84" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -15043,43 +15030,43 @@
         <v>258</v>
       </c>
       <c r="H85" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I85" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="J85" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B86" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C86" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="D86" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="E86" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F86" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="G86" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B87">
+      <c r="B87" s="32">
         <v>15</v>
       </c>
       <c r="C87" s="13">
@@ -15088,7 +15075,7 @@
       <c r="D87" s="13">
         <v>0.19736842105263158</v>
       </c>
-      <c r="E87">
+      <c r="E87" s="32">
         <v>11</v>
       </c>
       <c r="F87" s="13">
@@ -15097,7 +15084,7 @@
       <c r="G87" s="13">
         <v>0.29729729729729731</v>
       </c>
-      <c r="H87">
+      <c r="H87" s="32">
         <v>26</v>
       </c>
       <c r="I87" s="13">
@@ -15111,7 +15098,7 @@
       <c r="A88" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="B88">
+      <c r="B88" s="32">
         <v>1</v>
       </c>
       <c r="C88" s="13">
@@ -15120,13 +15107,14 @@
       <c r="D88" s="13">
         <v>1.3157894736842105E-2</v>
       </c>
+      <c r="E88" s="32"/>
       <c r="F88" s="13">
         <v>0</v>
       </c>
       <c r="G88" s="13">
         <v>0</v>
       </c>
-      <c r="H88">
+      <c r="H88" s="32">
         <v>1</v>
       </c>
       <c r="I88" s="13">
@@ -15140,7 +15128,7 @@
       <c r="A89" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="B89">
+      <c r="B89" s="32">
         <v>7</v>
       </c>
       <c r="C89" s="13">
@@ -15149,7 +15137,7 @@
       <c r="D89" s="13">
         <v>9.2105263157894732E-2</v>
       </c>
-      <c r="E89">
+      <c r="E89" s="32">
         <v>2</v>
       </c>
       <c r="F89" s="13">
@@ -15158,7 +15146,7 @@
       <c r="G89" s="13">
         <v>5.4054054054054057E-2</v>
       </c>
-      <c r="H89">
+      <c r="H89" s="32">
         <v>9</v>
       </c>
       <c r="I89" s="13">
@@ -15172,13 +15160,14 @@
       <c r="A90" s="11" t="s">
         <v>247</v>
       </c>
+      <c r="B90" s="32"/>
       <c r="C90" s="13">
         <v>0</v>
       </c>
       <c r="D90" s="13">
         <v>0</v>
       </c>
-      <c r="E90">
+      <c r="E90" s="32">
         <v>1</v>
       </c>
       <c r="F90" s="13">
@@ -15187,7 +15176,7 @@
       <c r="G90" s="13">
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="H90">
+      <c r="H90" s="32">
         <v>1</v>
       </c>
       <c r="I90" s="13">
@@ -15201,7 +15190,7 @@
       <c r="A91" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="B91">
+      <c r="B91" s="32">
         <v>1</v>
       </c>
       <c r="C91" s="13">
@@ -15210,13 +15199,14 @@
       <c r="D91" s="13">
         <v>1.3157894736842105E-2</v>
       </c>
+      <c r="E91" s="32"/>
       <c r="F91" s="13">
         <v>0</v>
       </c>
       <c r="G91" s="13">
         <v>0</v>
       </c>
-      <c r="H91">
+      <c r="H91" s="32">
         <v>1</v>
       </c>
       <c r="I91" s="13">
@@ -15230,7 +15220,7 @@
       <c r="A92" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="B92">
+      <c r="B92" s="32">
         <v>1</v>
       </c>
       <c r="C92" s="13">
@@ -15239,7 +15229,7 @@
       <c r="D92" s="13">
         <v>1.3157894736842105E-2</v>
       </c>
-      <c r="E92">
+      <c r="E92" s="32">
         <v>1</v>
       </c>
       <c r="F92" s="13">
@@ -15248,7 +15238,7 @@
       <c r="G92" s="13">
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="H92">
+      <c r="H92" s="32">
         <v>2</v>
       </c>
       <c r="I92" s="13">
@@ -15262,13 +15252,14 @@
       <c r="A93" s="11" t="s">
         <v>256</v>
       </c>
+      <c r="B93" s="32"/>
       <c r="C93" s="13">
         <v>0</v>
       </c>
       <c r="D93" s="13">
         <v>0</v>
       </c>
-      <c r="E93">
+      <c r="E93" s="32">
         <v>1</v>
       </c>
       <c r="F93" s="13">
@@ -15277,7 +15268,7 @@
       <c r="G93" s="13">
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="H93">
+      <c r="H93" s="32">
         <v>1</v>
       </c>
       <c r="I93" s="13">
@@ -15291,7 +15282,7 @@
       <c r="A94" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B94">
+      <c r="B94" s="32">
         <v>4</v>
       </c>
       <c r="C94" s="13">
@@ -15300,7 +15291,7 @@
       <c r="D94" s="13">
         <v>5.2631578947368418E-2</v>
       </c>
-      <c r="E94">
+      <c r="E94" s="32">
         <v>3</v>
       </c>
       <c r="F94" s="13">
@@ -15309,7 +15300,7 @@
       <c r="G94" s="13">
         <v>8.1081081081081086E-2</v>
       </c>
-      <c r="H94">
+      <c r="H94" s="32">
         <v>7</v>
       </c>
       <c r="I94" s="13">
@@ -15323,7 +15314,7 @@
       <c r="A95" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="B95">
+      <c r="B95" s="32">
         <v>1</v>
       </c>
       <c r="C95" s="13">
@@ -15332,7 +15323,7 @@
       <c r="D95" s="13">
         <v>1.3157894736842105E-2</v>
       </c>
-      <c r="E95">
+      <c r="E95" s="32">
         <v>3</v>
       </c>
       <c r="F95" s="13">
@@ -15341,7 +15332,7 @@
       <c r="G95" s="13">
         <v>8.1081081081081086E-2</v>
       </c>
-      <c r="H95">
+      <c r="H95" s="32">
         <v>4</v>
       </c>
       <c r="I95" s="13">
@@ -15355,7 +15346,7 @@
       <c r="A96" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B96">
+      <c r="B96" s="32">
         <v>26</v>
       </c>
       <c r="C96" s="13">
@@ -15364,7 +15355,7 @@
       <c r="D96" s="13">
         <v>0.34210526315789475</v>
       </c>
-      <c r="E96">
+      <c r="E96" s="32">
         <v>5</v>
       </c>
       <c r="F96" s="13">
@@ -15373,7 +15364,7 @@
       <c r="G96" s="13">
         <v>0.13513513513513514</v>
       </c>
-      <c r="H96">
+      <c r="H96" s="32">
         <v>31</v>
       </c>
       <c r="I96" s="13">
@@ -15387,7 +15378,7 @@
       <c r="A97" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="B97">
+      <c r="B97" s="32">
         <v>1</v>
       </c>
       <c r="C97" s="13">
@@ -15396,13 +15387,14 @@
       <c r="D97" s="13">
         <v>1.3157894736842105E-2</v>
       </c>
+      <c r="E97" s="32"/>
       <c r="F97" s="13">
         <v>0</v>
       </c>
       <c r="G97" s="13">
         <v>0</v>
       </c>
-      <c r="H97">
+      <c r="H97" s="32">
         <v>1</v>
       </c>
       <c r="I97" s="13">
@@ -15416,7 +15408,7 @@
       <c r="A98" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="B98">
+      <c r="B98" s="32">
         <v>20</v>
       </c>
       <c r="C98" s="13">
@@ -15425,7 +15417,7 @@
       <c r="D98" s="13">
         <v>0.26315789473684209</v>
       </c>
-      <c r="E98">
+      <c r="E98" s="32">
         <v>5</v>
       </c>
       <c r="F98" s="13">
@@ -15434,7 +15426,7 @@
       <c r="G98" s="13">
         <v>0.13513513513513514</v>
       </c>
-      <c r="H98">
+      <c r="H98" s="32">
         <v>25</v>
       </c>
       <c r="I98" s="13">
@@ -15448,7 +15440,7 @@
       <c r="A99" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="B99">
+      <c r="B99" s="32">
         <v>4</v>
       </c>
       <c r="C99" s="13">
@@ -15457,13 +15449,14 @@
       <c r="D99" s="13">
         <v>5.2631578947368418E-2</v>
       </c>
+      <c r="E99" s="32"/>
       <c r="F99" s="13">
         <v>0</v>
       </c>
       <c r="G99" s="13">
         <v>0</v>
       </c>
-      <c r="H99">
+      <c r="H99" s="32">
         <v>4</v>
       </c>
       <c r="I99" s="13">
@@ -15477,7 +15470,7 @@
       <c r="A100" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="B100">
+      <c r="B100" s="32">
         <v>1</v>
       </c>
       <c r="C100" s="13">
@@ -15486,13 +15479,14 @@
       <c r="D100" s="13">
         <v>1.3157894736842105E-2</v>
       </c>
+      <c r="E100" s="32"/>
       <c r="F100" s="13">
         <v>0</v>
       </c>
       <c r="G100" s="13">
         <v>0</v>
       </c>
-      <c r="H100">
+      <c r="H100" s="32">
         <v>1</v>
       </c>
       <c r="I100" s="13">
@@ -15506,7 +15500,7 @@
       <c r="A101" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B101">
+      <c r="B101" s="32">
         <v>10</v>
       </c>
       <c r="C101" s="13">
@@ -15515,7 +15509,7 @@
       <c r="D101" s="13">
         <v>0.13157894736842105</v>
       </c>
-      <c r="E101">
+      <c r="E101" s="32">
         <v>4</v>
       </c>
       <c r="F101" s="13">
@@ -15524,7 +15518,7 @@
       <c r="G101" s="13">
         <v>0.10810810810810811</v>
       </c>
-      <c r="H101">
+      <c r="H101" s="32">
         <v>14</v>
       </c>
       <c r="I101" s="13">
@@ -15538,7 +15532,7 @@
       <c r="A102" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="B102">
+      <c r="B102" s="32">
         <v>4</v>
       </c>
       <c r="C102" s="13">
@@ -15547,13 +15541,14 @@
       <c r="D102" s="13">
         <v>5.2631578947368418E-2</v>
       </c>
+      <c r="E102" s="32"/>
       <c r="F102" s="13">
         <v>0</v>
       </c>
       <c r="G102" s="13">
         <v>0</v>
       </c>
-      <c r="H102">
+      <c r="H102" s="32">
         <v>4</v>
       </c>
       <c r="I102" s="13">
@@ -15567,7 +15562,7 @@
       <c r="A103" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="B103">
+      <c r="B103" s="32">
         <v>4</v>
       </c>
       <c r="C103" s="13">
@@ -15576,7 +15571,7 @@
       <c r="D103" s="13">
         <v>5.2631578947368418E-2</v>
       </c>
-      <c r="E103">
+      <c r="E103" s="32">
         <v>1</v>
       </c>
       <c r="F103" s="13">
@@ -15585,7 +15580,7 @@
       <c r="G103" s="13">
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="H103">
+      <c r="H103" s="32">
         <v>5</v>
       </c>
       <c r="I103" s="13">
@@ -15599,7 +15594,7 @@
       <c r="A104" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="B104">
+      <c r="B104" s="32">
         <v>1</v>
       </c>
       <c r="C104" s="13">
@@ -15608,7 +15603,7 @@
       <c r="D104" s="13">
         <v>1.3157894736842105E-2</v>
       </c>
-      <c r="E104">
+      <c r="E104" s="32">
         <v>1</v>
       </c>
       <c r="F104" s="13">
@@ -15617,7 +15612,7 @@
       <c r="G104" s="13">
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="H104">
+      <c r="H104" s="32">
         <v>2</v>
       </c>
       <c r="I104" s="13">
@@ -15631,7 +15626,7 @@
       <c r="A105" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="B105">
+      <c r="B105" s="32">
         <v>1</v>
       </c>
       <c r="C105" s="13">
@@ -15640,7 +15635,7 @@
       <c r="D105" s="13">
         <v>1.3157894736842105E-2</v>
       </c>
-      <c r="E105">
+      <c r="E105" s="32">
         <v>1</v>
       </c>
       <c r="F105" s="13">
@@ -15649,7 +15644,7 @@
       <c r="G105" s="13">
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="H105">
+      <c r="H105" s="32">
         <v>2</v>
       </c>
       <c r="I105" s="13">
@@ -15663,13 +15658,14 @@
       <c r="A106" s="11" t="s">
         <v>252</v>
       </c>
+      <c r="B106" s="32"/>
       <c r="C106" s="13">
         <v>0</v>
       </c>
       <c r="D106" s="13">
         <v>0</v>
       </c>
-      <c r="E106">
+      <c r="E106" s="32">
         <v>1</v>
       </c>
       <c r="F106" s="13">
@@ -15678,7 +15674,7 @@
       <c r="G106" s="13">
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="H106">
+      <c r="H106" s="32">
         <v>1</v>
       </c>
       <c r="I106" s="13">
@@ -15692,7 +15688,7 @@
       <c r="A107" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B107">
+      <c r="B107" s="32">
         <v>7</v>
       </c>
       <c r="C107" s="13">
@@ -15701,7 +15697,7 @@
       <c r="D107" s="13">
         <v>9.2105263157894732E-2</v>
       </c>
-      <c r="E107">
+      <c r="E107" s="32">
         <v>1</v>
       </c>
       <c r="F107" s="13">
@@ -15710,7 +15706,7 @@
       <c r="G107" s="13">
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="H107">
+      <c r="H107" s="32">
         <v>8</v>
       </c>
       <c r="I107" s="13">
@@ -15724,7 +15720,7 @@
       <c r="A108" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="B108">
+      <c r="B108" s="32">
         <v>7</v>
       </c>
       <c r="C108" s="13">
@@ -15733,7 +15729,7 @@
       <c r="D108" s="13">
         <v>9.2105263157894732E-2</v>
       </c>
-      <c r="E108">
+      <c r="E108" s="32">
         <v>1</v>
       </c>
       <c r="F108" s="13">
@@ -15742,7 +15738,7 @@
       <c r="G108" s="13">
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="H108">
+      <c r="H108" s="32">
         <v>8</v>
       </c>
       <c r="I108" s="13">
@@ -15756,7 +15752,7 @@
       <c r="A109" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B109">
+      <c r="B109" s="32">
         <v>2</v>
       </c>
       <c r="C109" s="13">
@@ -15765,7 +15761,7 @@
       <c r="D109" s="13">
         <v>2.6315789473684209E-2</v>
       </c>
-      <c r="E109">
+      <c r="E109" s="32">
         <v>3</v>
       </c>
       <c r="F109" s="13">
@@ -15774,7 +15770,7 @@
       <c r="G109" s="13">
         <v>8.1081081081081086E-2</v>
       </c>
-      <c r="H109">
+      <c r="H109" s="32">
         <v>5</v>
       </c>
       <c r="I109" s="13">
@@ -15788,7 +15784,7 @@
       <c r="A110" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="B110">
+      <c r="B110" s="32">
         <v>2</v>
       </c>
       <c r="C110" s="13">
@@ -15797,7 +15793,7 @@
       <c r="D110" s="13">
         <v>2.6315789473684209E-2</v>
       </c>
-      <c r="E110">
+      <c r="E110" s="32">
         <v>3</v>
       </c>
       <c r="F110" s="13">
@@ -15806,7 +15802,7 @@
       <c r="G110" s="13">
         <v>8.1081081081081086E-2</v>
       </c>
-      <c r="H110">
+      <c r="H110" s="32">
         <v>5</v>
       </c>
       <c r="I110" s="13">
@@ -15820,7 +15816,7 @@
       <c r="A111" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B111">
+      <c r="B111" s="32">
         <v>10</v>
       </c>
       <c r="C111" s="13">
@@ -15829,7 +15825,7 @@
       <c r="D111" s="13">
         <v>0.13157894736842105</v>
       </c>
-      <c r="E111">
+      <c r="E111" s="32">
         <v>9</v>
       </c>
       <c r="F111" s="13">
@@ -15838,7 +15834,7 @@
       <c r="G111" s="13">
         <v>0.24324324324324326</v>
       </c>
-      <c r="H111">
+      <c r="H111" s="32">
         <v>19</v>
       </c>
       <c r="I111" s="13">
@@ -15852,7 +15848,7 @@
       <c r="A112" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="B112">
+      <c r="B112" s="32">
         <v>1</v>
       </c>
       <c r="C112" s="13">
@@ -15861,13 +15857,14 @@
       <c r="D112" s="13">
         <v>1.3157894736842105E-2</v>
       </c>
+      <c r="E112" s="32"/>
       <c r="F112" s="13">
         <v>0</v>
       </c>
       <c r="G112" s="13">
         <v>0</v>
       </c>
-      <c r="H112">
+      <c r="H112" s="32">
         <v>1</v>
       </c>
       <c r="I112" s="13">
@@ -15881,7 +15878,7 @@
       <c r="A113" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="B113">
+      <c r="B113" s="32">
         <v>1</v>
       </c>
       <c r="C113" s="13">
@@ -15890,7 +15887,7 @@
       <c r="D113" s="13">
         <v>1.3157894736842105E-2</v>
       </c>
-      <c r="E113">
+      <c r="E113" s="32">
         <v>1</v>
       </c>
       <c r="F113" s="13">
@@ -15899,7 +15896,7 @@
       <c r="G113" s="13">
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="H113">
+      <c r="H113" s="32">
         <v>2</v>
       </c>
       <c r="I113" s="13">
@@ -15913,7 +15910,7 @@
       <c r="A114" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="B114">
+      <c r="B114" s="32">
         <v>4</v>
       </c>
       <c r="C114" s="13">
@@ -15922,7 +15919,7 @@
       <c r="D114" s="13">
         <v>5.2631578947368418E-2</v>
       </c>
-      <c r="E114">
+      <c r="E114" s="32">
         <v>4</v>
       </c>
       <c r="F114" s="13">
@@ -15931,7 +15928,7 @@
       <c r="G114" s="13">
         <v>0.10810810810810811</v>
       </c>
-      <c r="H114">
+      <c r="H114" s="32">
         <v>8</v>
       </c>
       <c r="I114" s="13">
@@ -15945,13 +15942,14 @@
       <c r="A115" s="11" t="s">
         <v>239</v>
       </c>
+      <c r="B115" s="32"/>
       <c r="C115" s="13">
         <v>0</v>
       </c>
       <c r="D115" s="13">
         <v>0</v>
       </c>
-      <c r="E115">
+      <c r="E115" s="32">
         <v>4</v>
       </c>
       <c r="F115" s="13">
@@ -15960,7 +15958,7 @@
       <c r="G115" s="13">
         <v>0.10810810810810811</v>
       </c>
-      <c r="H115">
+      <c r="H115" s="32">
         <v>4</v>
       </c>
       <c r="I115" s="13">
@@ -15974,7 +15972,7 @@
       <c r="A116" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="B116">
+      <c r="B116" s="32">
         <v>4</v>
       </c>
       <c r="C116" s="13">
@@ -15983,13 +15981,14 @@
       <c r="D116" s="13">
         <v>5.2631578947368418E-2</v>
       </c>
+      <c r="E116" s="32"/>
       <c r="F116" s="13">
         <v>0</v>
       </c>
       <c r="G116" s="13">
         <v>0</v>
       </c>
-      <c r="H116">
+      <c r="H116" s="32">
         <v>4</v>
       </c>
       <c r="I116" s="13">
@@ -16003,7 +16002,7 @@
       <c r="A117" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B117">
+      <c r="B117" s="32">
         <v>6</v>
       </c>
       <c r="C117" s="13">
@@ -16012,7 +16011,7 @@
       <c r="D117" s="13">
         <v>7.8947368421052627E-2</v>
       </c>
-      <c r="E117">
+      <c r="E117" s="32">
         <v>4</v>
       </c>
       <c r="F117" s="13">
@@ -16021,7 +16020,7 @@
       <c r="G117" s="13">
         <v>0.10810810810810811</v>
       </c>
-      <c r="H117">
+      <c r="H117" s="32">
         <v>10</v>
       </c>
       <c r="I117" s="13">
@@ -16035,7 +16034,7 @@
       <c r="A118" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="B118">
+      <c r="B118" s="32">
         <v>3</v>
       </c>
       <c r="C118" s="13">
@@ -16044,7 +16043,7 @@
       <c r="D118" s="13">
         <v>3.9473684210526314E-2</v>
       </c>
-      <c r="E118">
+      <c r="E118" s="32">
         <v>1</v>
       </c>
       <c r="F118" s="13">
@@ -16053,7 +16052,7 @@
       <c r="G118" s="13">
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="H118">
+      <c r="H118" s="32">
         <v>4</v>
       </c>
       <c r="I118" s="13">
@@ -16067,7 +16066,7 @@
       <c r="A119" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="B119">
+      <c r="B119" s="32">
         <v>1</v>
       </c>
       <c r="C119" s="13">
@@ -16076,7 +16075,7 @@
       <c r="D119" s="13">
         <v>1.3157894736842105E-2</v>
       </c>
-      <c r="E119">
+      <c r="E119" s="32">
         <v>1</v>
       </c>
       <c r="F119" s="13">
@@ -16085,7 +16084,7 @@
       <c r="G119" s="13">
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="H119">
+      <c r="H119" s="32">
         <v>2</v>
       </c>
       <c r="I119" s="13">
@@ -16099,7 +16098,7 @@
       <c r="A120" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="B120">
+      <c r="B120" s="32">
         <v>2</v>
       </c>
       <c r="C120" s="13">
@@ -16108,7 +16107,7 @@
       <c r="D120" s="13">
         <v>2.6315789473684209E-2</v>
       </c>
-      <c r="E120">
+      <c r="E120" s="32">
         <v>2</v>
       </c>
       <c r="F120" s="13">
@@ -16117,7 +16116,7 @@
       <c r="G120" s="13">
         <v>5.4054054054054057E-2</v>
       </c>
-      <c r="H120">
+      <c r="H120" s="32">
         <v>4</v>
       </c>
       <c r="I120" s="13">
@@ -16129,9 +16128,9 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="B121">
+        <v>290</v>
+      </c>
+      <c r="B121" s="32">
         <v>76</v>
       </c>
       <c r="C121" s="13">
@@ -16140,7 +16139,7 @@
       <c r="D121" s="13">
         <v>1</v>
       </c>
-      <c r="E121">
+      <c r="E121" s="32">
         <v>37</v>
       </c>
       <c r="F121" s="13">
@@ -16149,7 +16148,7 @@
       <c r="G121" s="13">
         <v>1</v>
       </c>
-      <c r="H121">
+      <c r="H121" s="32">
         <v>113</v>
       </c>
       <c r="I121" s="13">
@@ -16160,23 +16159,23 @@
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A126" s="27" t="s">
-        <v>317</v>
-      </c>
-      <c r="B126" s="27"/>
-      <c r="C126" s="27"/>
+      <c r="A126" s="29" t="s">
+        <v>311</v>
+      </c>
+      <c r="B126" s="29"/>
+      <c r="C126" s="29"/>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A127" s="27"/>
-      <c r="B127" s="27"/>
-      <c r="C127" s="27"/>
+      <c r="A127" s="29"/>
+      <c r="B127" s="29"/>
+      <c r="C127" s="29"/>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B128" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
@@ -16184,22 +16183,22 @@
         <v>4</v>
       </c>
       <c r="B129" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B131" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B132">
+      <c r="B132" s="32">
         <v>16</v>
       </c>
     </row>
@@ -16207,7 +16206,7 @@
       <c r="A133" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="B133">
+      <c r="B133" s="32">
         <v>9</v>
       </c>
     </row>
@@ -16215,7 +16214,7 @@
       <c r="A134" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B134">
+      <c r="B134" s="32">
         <v>7</v>
       </c>
       <c r="E134" s="15"/>
@@ -16226,7 +16225,7 @@
       <c r="A135" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B135">
+      <c r="B135" s="32">
         <v>25</v>
       </c>
       <c r="E135" s="15"/>
@@ -16237,7 +16236,7 @@
       <c r="A136" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="B136">
+      <c r="B136" s="32">
         <v>25</v>
       </c>
     </row>
@@ -16245,7 +16244,7 @@
       <c r="A137" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B137">
+      <c r="B137" s="32">
         <v>5</v>
       </c>
     </row>
@@ -16253,7 +16252,7 @@
       <c r="A138" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="B138">
+      <c r="B138" s="32">
         <v>5</v>
       </c>
     </row>
@@ -16261,7 +16260,7 @@
       <c r="A139" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B139">
+      <c r="B139" s="32">
         <v>8</v>
       </c>
     </row>
@@ -16269,7 +16268,7 @@
       <c r="A140" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="B140">
+      <c r="B140" s="32">
         <v>8</v>
       </c>
     </row>
@@ -16277,7 +16276,7 @@
       <c r="A141" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B141">
+      <c r="B141" s="32">
         <v>5</v>
       </c>
     </row>
@@ -16285,7 +16284,7 @@
       <c r="A142" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="B142">
+      <c r="B142" s="32">
         <v>5</v>
       </c>
     </row>
@@ -16293,7 +16292,7 @@
       <c r="A143" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B143">
+      <c r="B143" s="32">
         <v>8</v>
       </c>
     </row>
@@ -16301,15 +16300,15 @@
       <c r="A144" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="B144">
+      <c r="B144" s="32">
         <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="B145">
+        <v>290</v>
+      </c>
+      <c r="B145" s="32">
         <v>67</v>
       </c>
     </row>
@@ -16319,8 +16318,8 @@
     <mergeCell ref="A47:K48"/>
     <mergeCell ref="A126:C127"/>
     <mergeCell ref="C7:E8"/>
-    <mergeCell ref="H7:J8"/>
-    <mergeCell ref="C5:J6"/>
+    <mergeCell ref="C5:K6"/>
+    <mergeCell ref="H7:K8"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B51">
@@ -16377,14 +16376,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
@@ -16400,7 +16399,7 @@
         <v>277</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>279</v>
@@ -16423,7 +16422,7 @@
         <v>280</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -16440,10 +16439,10 @@
         <v>14</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>280</v>
+        <v>317</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -16463,7 +16462,7 @@
         <v>280</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -16474,7 +16473,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>260</v>
@@ -16483,7 +16482,7 @@
         <v>281</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -16537,11 +16536,11 @@
       <c r="D9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>305</v>
+      <c r="E9" s="35" t="s">
+        <v>318</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -16554,10 +16553,10 @@
         <v>15</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>283</v>
+        <v>316</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -16570,10 +16569,10 @@
         <v>15</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -16610,7 +16609,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
